--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vunl-my.sharepoint.com/personal/clara_miguelsanz_vu_nl/Documents/Metapsy project/METAPSY INTERNAL FOLDER/Databases/Eating disorders (cbt and non-cbt)/digital-interventions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniasprenger/Documents/Git/metapsy-project/data-ed-digital-psyctr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2060" documentId="8_{6A994463-6F37-4872-A4CA-EEFECD33D8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F9E780-AE5F-C64C-B88C-DA6837AB84D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCC9A24-1173-5A4C-8964-EE9E952CE2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="620" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29780" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -38,41 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Variables in grey: mandatory for metapsyTools to work. Variables with a dot in from (e.g., .g) are added by the metapsyTools package after calculating effect sizes
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">	-C Miguel Sanz</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6595" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6604" uniqueCount="474">
   <si>
     <t>study</t>
   </si>
@@ -1507,16 +1474,47 @@
   <si>
     <t>panas-p</t>
   </si>
+  <si>
+    <t>Contains studies up to:</t>
+  </si>
+  <si>
+    <t>Rated by two reviewers:</t>
+  </si>
+  <si>
+    <t>RoB tool:</t>
+  </si>
+  <si>
+    <t>Comparison(s):</t>
+  </si>
+  <si>
+    <t>timepoints:</t>
+  </si>
+  <si>
+    <t>RoB-1</t>
+  </si>
+  <si>
+    <t>PSY vs CTR</t>
+  </si>
+  <si>
+    <t>Post and FU</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1600,12 +1598,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1631,8 +1623,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1673,12 +1672,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
         <bgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1746,93 +1739,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2047,11 +2043,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BI385"/>
+  <dimension ref="A1:BI386"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" style="26" customWidth="1"/>
@@ -9137,16 +9133,16 @@
       <c r="F80" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G80" s="26" t="s">
+      <c r="G80" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H80" s="26" t="s">
+      <c r="H80" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I80" s="26" t="s">
+      <c r="I80" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J80" s="26" t="s">
+      <c r="J80" s="39" t="s">
         <v>316</v>
       </c>
       <c r="K80" s="26" t="s">
@@ -9223,13 +9219,13 @@
       <c r="G81" s="39" t="s">
         <v>464</v>
       </c>
-      <c r="H81" s="26" t="s">
+      <c r="H81" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I81" s="26" t="s">
+      <c r="I81" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="J81" s="26" t="s">
+      <c r="J81" s="39" t="s">
         <v>316</v>
       </c>
       <c r="K81" s="26" t="s">
@@ -9306,13 +9302,13 @@
       <c r="G82" s="39" t="s">
         <v>465</v>
       </c>
-      <c r="H82" s="26" t="s">
+      <c r="H82" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I82" s="26" t="s">
+      <c r="I82" s="39" t="s">
         <v>313</v>
       </c>
-      <c r="J82" s="26" t="s">
+      <c r="J82" s="39" t="s">
         <v>316</v>
       </c>
       <c r="K82" s="26" t="s">
@@ -9386,16 +9382,16 @@
       <c r="F83" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G83" s="26" t="s">
+      <c r="G83" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H83" s="26" t="s">
+      <c r="H83" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I83" s="26" t="s">
+      <c r="I83" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J83" s="26" t="s">
+      <c r="J83" s="39" t="s">
         <v>316</v>
       </c>
       <c r="K83" s="26" t="s">
@@ -9469,16 +9465,16 @@
       <c r="F84" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G84" s="26" t="s">
+      <c r="G84" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="H84" s="26" t="s">
+      <c r="H84" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I84" s="26" t="s">
+      <c r="I84" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J84" s="26">
+      <c r="J84" s="39">
         <v>8</v>
       </c>
       <c r="K84" s="26" t="s">
@@ -9552,16 +9548,16 @@
       <c r="F85" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G85" s="26" t="s">
+      <c r="G85" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H85" s="26" t="s">
+      <c r="H85" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I85" s="26" t="s">
+      <c r="I85" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J85" s="26">
+      <c r="J85" s="39">
         <v>8</v>
       </c>
       <c r="K85" s="26" t="s">
@@ -9635,16 +9631,16 @@
       <c r="F86" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G86" s="26" t="s">
+      <c r="G86" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H86" s="26" t="s">
+      <c r="H86" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I86" s="26" t="s">
+      <c r="I86" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J86" s="26">
+      <c r="J86" s="39">
         <v>8</v>
       </c>
       <c r="K86" s="26" t="s">
@@ -9721,13 +9717,13 @@
       <c r="G87" s="39" t="s">
         <v>464</v>
       </c>
-      <c r="H87" s="26" t="s">
+      <c r="H87" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I87" s="26" t="s">
+      <c r="I87" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="J87" s="26">
+      <c r="J87" s="39">
         <v>8</v>
       </c>
       <c r="K87" s="26" t="s">
@@ -9804,13 +9800,13 @@
       <c r="G88" s="39" t="s">
         <v>465</v>
       </c>
-      <c r="H88" s="26" t="s">
+      <c r="H88" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I88" s="26" t="s">
+      <c r="I88" s="39" t="s">
         <v>313</v>
       </c>
-      <c r="J88" s="26">
+      <c r="J88" s="39">
         <v>8</v>
       </c>
       <c r="K88" s="26" t="s">
@@ -9884,16 +9880,16 @@
       <c r="F89" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G89" s="26" t="s">
+      <c r="G89" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H89" s="26" t="s">
+      <c r="H89" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I89" s="26" t="s">
+      <c r="I89" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J89" s="26">
+      <c r="J89" s="39">
         <v>8</v>
       </c>
       <c r="K89" s="26" t="s">
@@ -9967,16 +9963,16 @@
       <c r="F90" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G90" s="26" t="s">
+      <c r="G90" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="H90" s="26" t="s">
+      <c r="H90" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I90" s="26" t="s">
+      <c r="I90" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J90" s="26">
+      <c r="J90" s="39">
         <v>12</v>
       </c>
       <c r="K90" s="26" t="s">
@@ -10053,16 +10049,16 @@
       <c r="F91" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G91" s="26" t="s">
+      <c r="G91" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="H91" s="26" t="s">
+      <c r="H91" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I91" s="26" t="s">
+      <c r="I91" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J91" s="26">
+      <c r="J91" s="39">
         <v>12</v>
       </c>
       <c r="K91" s="26" t="s">
@@ -10139,16 +10135,16 @@
       <c r="F92" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G92" s="26" t="s">
+      <c r="G92" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H92" s="26" t="s">
+      <c r="H92" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I92" s="26" t="s">
+      <c r="I92" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J92" s="26">
+      <c r="J92" s="39">
         <v>12</v>
       </c>
       <c r="K92" s="26" t="s">
@@ -10225,16 +10221,16 @@
       <c r="F93" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G93" s="26" t="s">
+      <c r="G93" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H93" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I93" s="26" t="s">
+      <c r="I93" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J93" s="26">
+      <c r="J93" s="39">
         <v>12</v>
       </c>
       <c r="K93" s="26" t="s">
@@ -10311,16 +10307,16 @@
       <c r="F94" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="26" t="s">
+      <c r="G94" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H94" s="26" t="s">
+      <c r="H94" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I94" s="26" t="s">
+      <c r="I94" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J94" s="26">
+      <c r="J94" s="39">
         <v>12</v>
       </c>
       <c r="K94" s="26" t="s">
@@ -10397,16 +10393,16 @@
       <c r="F95" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G95" s="26" t="s">
+      <c r="G95" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="H95" s="26" t="s">
+      <c r="H95" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I95" s="26" t="s">
+      <c r="I95" s="39" t="s">
         <v>323</v>
       </c>
-      <c r="J95" s="26">
+      <c r="J95" s="39">
         <v>12</v>
       </c>
       <c r="K95" s="26" t="s">
@@ -10483,16 +10479,16 @@
       <c r="F96" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G96" s="26" t="s">
+      <c r="G96" s="39" t="s">
         <v>322</v>
       </c>
-      <c r="H96" s="26" t="s">
+      <c r="H96" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I96" s="26" t="s">
+      <c r="I96" s="39" t="s">
         <v>323</v>
       </c>
-      <c r="J96" s="26">
+      <c r="J96" s="39">
         <v>12</v>
       </c>
       <c r="K96" s="26" t="s">
@@ -10569,16 +10565,16 @@
       <c r="F97" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G97" s="26" t="s">
+      <c r="G97" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="H97" s="26" t="s">
+      <c r="H97" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I97" s="26" t="s">
+      <c r="I97" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J97" s="26">
+      <c r="J97" s="39">
         <v>12</v>
       </c>
       <c r="K97" s="26" t="s">
@@ -10655,16 +10651,16 @@
       <c r="F98" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G98" s="26" t="s">
+      <c r="G98" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="H98" s="26" t="s">
+      <c r="H98" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I98" s="26" t="s">
+      <c r="I98" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J98" s="26">
+      <c r="J98" s="39">
         <v>12</v>
       </c>
       <c r="K98" s="26" t="s">
@@ -10741,16 +10737,16 @@
       <c r="F99" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G99" s="26" t="s">
+      <c r="G99" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H99" s="26" t="s">
+      <c r="H99" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I99" s="26" t="s">
+      <c r="I99" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J99" s="26">
+      <c r="J99" s="39">
         <v>12</v>
       </c>
       <c r="K99" s="26" t="s">
@@ -10827,16 +10823,16 @@
       <c r="F100" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G100" s="26" t="s">
+      <c r="G100" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H100" s="26" t="s">
+      <c r="H100" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I100" s="26" t="s">
+      <c r="I100" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J100" s="26">
+      <c r="J100" s="39">
         <v>12</v>
       </c>
       <c r="K100" s="26" t="s">
@@ -10913,16 +10909,16 @@
       <c r="F101" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G101" s="26" t="s">
+      <c r="G101" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H101" s="26" t="s">
+      <c r="H101" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I101" s="26" t="s">
+      <c r="I101" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J101" s="26">
+      <c r="J101" s="39">
         <v>12</v>
       </c>
       <c r="K101" s="26" t="s">
@@ -10999,16 +10995,16 @@
       <c r="F102" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G102" s="26" t="s">
+      <c r="G102" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H102" s="26" t="s">
+      <c r="H102" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I102" s="26" t="s">
+      <c r="I102" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J102" s="26">
+      <c r="J102" s="39">
         <v>12</v>
       </c>
       <c r="K102" s="26" t="s">
@@ -11085,16 +11081,16 @@
       <c r="F103" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G103" s="26" t="s">
+      <c r="G103" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="H103" s="26" t="s">
+      <c r="H103" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I103" s="26" t="s">
+      <c r="I103" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J103" s="26">
+      <c r="J103" s="39">
         <v>12</v>
       </c>
       <c r="K103" s="26" t="s">
@@ -11171,16 +11167,16 @@
       <c r="F104" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G104" s="26" t="s">
+      <c r="G104" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H104" s="26" t="s">
+      <c r="H104" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I104" s="26" t="s">
+      <c r="I104" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J104" s="26">
+      <c r="J104" s="39">
         <v>12</v>
       </c>
       <c r="K104" s="26" t="s">
@@ -11263,16 +11259,16 @@
       <c r="F105" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G105" s="26" t="s">
+      <c r="G105" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H105" s="26" t="s">
+      <c r="H105" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I105" s="26" t="s">
+      <c r="I105" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J105" s="26">
+      <c r="J105" s="39">
         <v>8</v>
       </c>
       <c r="K105" s="26" t="s">
@@ -11352,16 +11348,16 @@
       <c r="F106" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G106" s="26" t="s">
+      <c r="G106" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H106" s="26" t="s">
+      <c r="H106" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I106" s="26" t="s">
+      <c r="I106" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J106" s="26">
+      <c r="J106" s="39">
         <v>8</v>
       </c>
       <c r="K106" s="26" t="s">
@@ -11441,16 +11437,16 @@
       <c r="F107" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G107" s="26" t="s">
+      <c r="G107" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H107" s="26" t="s">
+      <c r="H107" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I107" s="26" t="s">
+      <c r="I107" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J107" s="26">
+      <c r="J107" s="39">
         <v>8</v>
       </c>
       <c r="K107" s="26" t="s">
@@ -11530,16 +11526,16 @@
       <c r="F108" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G108" s="26" t="s">
+      <c r="G108" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H108" s="26" t="s">
+      <c r="H108" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I108" s="26" t="s">
+      <c r="I108" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J108" s="26">
+      <c r="J108" s="39">
         <v>8</v>
       </c>
       <c r="K108" s="26" t="s">
@@ -11613,16 +11609,16 @@
       <c r="F109" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G109" s="26" t="s">
+      <c r="G109" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H109" s="26" t="s">
+      <c r="H109" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I109" s="26" t="s">
+      <c r="I109" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J109" s="26">
+      <c r="J109" s="39">
         <v>8</v>
       </c>
       <c r="K109" s="26" t="s">
@@ -11696,16 +11692,16 @@
       <c r="F110" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G110" s="26" t="s">
+      <c r="G110" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H110" s="26" t="s">
+      <c r="H110" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I110" s="26" t="s">
+      <c r="I110" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J110" s="26">
+      <c r="J110" s="39">
         <v>8</v>
       </c>
       <c r="K110" s="26" t="s">
@@ -11779,16 +11775,16 @@
       <c r="F111" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G111" s="26" t="s">
+      <c r="G111" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H111" s="26" t="s">
+      <c r="H111" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I111" s="26" t="s">
+      <c r="I111" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J111" s="26">
+      <c r="J111" s="39">
         <v>8</v>
       </c>
       <c r="K111" s="26" t="s">
@@ -11862,16 +11858,16 @@
       <c r="F112" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G112" s="26" t="s">
+      <c r="G112" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H112" s="26" t="s">
+      <c r="H112" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I112" s="26" t="s">
+      <c r="I112" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J112" s="26">
+      <c r="J112" s="39">
         <v>8</v>
       </c>
       <c r="K112" s="26" t="s">
@@ -11945,16 +11941,16 @@
       <c r="F113" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G113" s="26" t="s">
+      <c r="G113" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="H113" s="26" t="s">
+      <c r="H113" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I113" s="26" t="s">
+      <c r="I113" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="J113" s="26">
+      <c r="J113" s="39">
         <v>8</v>
       </c>
       <c r="K113" s="26" t="s">
@@ -12028,16 +12024,16 @@
       <c r="F114" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G114" s="26" t="s">
+      <c r="G114" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H114" s="26" t="s">
+      <c r="H114" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I114" s="26" t="s">
+      <c r="I114" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J114" s="26">
+      <c r="J114" s="39">
         <v>8</v>
       </c>
       <c r="K114" s="26" t="s">
@@ -12111,13 +12107,13 @@
       <c r="F115" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G115" s="26" t="s">
+      <c r="G115" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="H115" s="26" t="s">
+      <c r="H115" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I115" s="26" t="s">
+      <c r="I115" s="39" t="s">
         <v>277</v>
       </c>
       <c r="J115" s="39">
@@ -12188,16 +12184,16 @@
       <c r="F116" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G116" s="26" t="s">
+      <c r="G116" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="H116" s="26" t="s">
+      <c r="H116" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I116" s="26" t="s">
+      <c r="I116" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J116" s="26">
+      <c r="J116" s="39">
         <v>8</v>
       </c>
       <c r="K116" s="26" t="s">
@@ -12271,16 +12267,16 @@
       <c r="F117" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G117" s="26" t="s">
+      <c r="G117" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H117" s="26" t="s">
+      <c r="H117" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I117" s="26" t="s">
+      <c r="I117" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J117" s="26">
+      <c r="J117" s="39">
         <v>8</v>
       </c>
       <c r="K117" s="26" t="s">
@@ -12357,13 +12353,13 @@
       <c r="G118" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H118" s="26" t="s">
+      <c r="H118" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I118" s="26" t="s">
+      <c r="I118" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J118" s="26">
+      <c r="J118" s="39">
         <v>8</v>
       </c>
       <c r="K118" s="26" t="s">
@@ -12440,13 +12436,13 @@
       <c r="G119" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H119" s="26" t="s">
+      <c r="H119" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I119" s="26" t="s">
+      <c r="I119" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J119" s="26">
+      <c r="J119" s="39">
         <v>8</v>
       </c>
       <c r="K119" s="26" t="s">
@@ -12520,16 +12516,16 @@
       <c r="F120" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G120" s="26" t="s">
+      <c r="G120" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H120" s="26" t="s">
+      <c r="H120" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I120" s="26" t="s">
+      <c r="I120" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J120" s="26">
+      <c r="J120" s="39">
         <v>8</v>
       </c>
       <c r="K120" s="26" t="s">
@@ -12603,16 +12599,16 @@
       <c r="F121" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G121" s="26" t="s">
+      <c r="G121" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="H121" s="26" t="s">
+      <c r="H121" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I121" s="26" t="s">
+      <c r="I121" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J121" s="26">
+      <c r="J121" s="39">
         <v>8</v>
       </c>
       <c r="K121" s="26" t="s">
@@ -12689,13 +12685,13 @@
       <c r="G122" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H122" s="26" t="s">
+      <c r="H122" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I122" s="26" t="s">
+      <c r="I122" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J122" s="26">
+      <c r="J122" s="39">
         <v>8</v>
       </c>
       <c r="K122" s="26" t="s">
@@ -12772,13 +12768,13 @@
       <c r="G123" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H123" s="26" t="s">
+      <c r="H123" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I123" s="26" t="s">
+      <c r="I123" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J123" s="26">
+      <c r="J123" s="39">
         <v>8</v>
       </c>
       <c r="K123" s="26" t="s">
@@ -12852,16 +12848,16 @@
       <c r="F124" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G124" s="26" t="s">
+      <c r="G124" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H124" s="26" t="s">
+      <c r="H124" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I124" s="26" t="s">
+      <c r="I124" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J124" s="26">
+      <c r="J124" s="39">
         <v>8</v>
       </c>
       <c r="K124" s="26" t="s">
@@ -12935,16 +12931,16 @@
       <c r="F125" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G125" s="26" t="s">
+      <c r="G125" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H125" s="26" t="s">
+      <c r="H125" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I125" s="26" t="s">
+      <c r="I125" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J125" s="26">
+      <c r="J125" s="39">
         <v>8</v>
       </c>
       <c r="K125" s="26" t="s">
@@ -13018,16 +13014,16 @@
       <c r="F126" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G126" s="26" t="s">
+      <c r="G126" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="H126" s="26" t="s">
+      <c r="H126" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I126" s="26" t="s">
+      <c r="I126" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J126" s="26">
+      <c r="J126" s="39">
         <v>24</v>
       </c>
       <c r="K126" s="26" t="s">
@@ -13095,16 +13091,16 @@
       <c r="F127" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G127" s="26" t="s">
+      <c r="G127" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="H127" s="26" t="s">
+      <c r="H127" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I127" s="26" t="s">
+      <c r="I127" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J127" s="26">
+      <c r="J127" s="39">
         <v>24</v>
       </c>
       <c r="K127" s="26" t="s">
@@ -13178,16 +13174,16 @@
       <c r="F128" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G128" s="26" t="s">
+      <c r="G128" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H128" s="26" t="s">
+      <c r="H128" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I128" s="26" t="s">
+      <c r="I128" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J128" s="26">
+      <c r="J128" s="39">
         <v>24</v>
       </c>
       <c r="K128" s="26" t="s">
@@ -13264,13 +13260,13 @@
       <c r="G129" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H129" s="26" t="s">
+      <c r="H129" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I129" s="26" t="s">
+      <c r="I129" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J129" s="26">
+      <c r="J129" s="39">
         <v>24</v>
       </c>
       <c r="K129" s="26" t="s">
@@ -13347,13 +13343,13 @@
       <c r="G130" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H130" s="26" t="s">
+      <c r="H130" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I130" s="26" t="s">
+      <c r="I130" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J130" s="26">
+      <c r="J130" s="39">
         <v>24</v>
       </c>
       <c r="K130" s="26" t="s">
@@ -13427,16 +13423,16 @@
       <c r="F131" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G131" s="26" t="s">
+      <c r="G131" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H131" s="26" t="s">
+      <c r="H131" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I131" s="26" t="s">
+      <c r="I131" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J131" s="26">
+      <c r="J131" s="39">
         <v>24</v>
       </c>
       <c r="K131" s="26" t="s">
@@ -13510,16 +13506,16 @@
       <c r="F132" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G132" s="26" t="s">
+      <c r="G132" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="H132" s="26" t="s">
+      <c r="H132" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I132" s="26" t="s">
+      <c r="I132" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J132" s="26">
+      <c r="J132" s="39">
         <v>24</v>
       </c>
       <c r="K132" s="26" t="s">
@@ -13596,13 +13592,13 @@
       <c r="G133" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H133" s="26" t="s">
+      <c r="H133" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I133" s="26" t="s">
+      <c r="I133" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J133" s="26">
+      <c r="J133" s="39">
         <v>24</v>
       </c>
       <c r="K133" s="26" t="s">
@@ -13679,13 +13675,13 @@
       <c r="G134" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H134" s="26" t="s">
+      <c r="H134" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I134" s="26" t="s">
+      <c r="I134" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J134" s="26">
+      <c r="J134" s="39">
         <v>24</v>
       </c>
       <c r="K134" s="26" t="s">
@@ -13759,16 +13755,16 @@
       <c r="F135" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G135" s="26" t="s">
+      <c r="G135" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H135" s="26" t="s">
+      <c r="H135" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I135" s="26" t="s">
+      <c r="I135" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J135" s="26">
+      <c r="J135" s="39">
         <v>24</v>
       </c>
       <c r="K135" s="26" t="s">
@@ -13845,13 +13841,13 @@
       <c r="G136" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H136" s="26" t="s">
+      <c r="H136" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I136" s="26" t="s">
+      <c r="I136" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J136" s="26">
+      <c r="J136" s="39">
         <v>24</v>
       </c>
       <c r="K136" s="26" t="s">
@@ -13928,13 +13924,13 @@
       <c r="G137" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="H137" s="26" t="s">
+      <c r="H137" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I137" s="26" t="s">
+      <c r="I137" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J137" s="26">
+      <c r="J137" s="39">
         <v>6</v>
       </c>
       <c r="K137" s="26" t="s">
@@ -14011,13 +14007,13 @@
       <c r="G138" s="39" t="s">
         <v>458</v>
       </c>
-      <c r="H138" s="26" t="s">
+      <c r="H138" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I138" s="26" t="s">
+      <c r="I138" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="J138" s="26">
+      <c r="J138" s="39">
         <v>6</v>
       </c>
       <c r="K138" s="26" t="s">
@@ -14094,13 +14090,13 @@
       <c r="G139" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="H139" s="26" t="s">
+      <c r="H139" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I139" s="26" t="s">
+      <c r="I139" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J139" s="26">
+      <c r="J139" s="39">
         <v>6</v>
       </c>
       <c r="K139" s="26" t="s">
@@ -14174,16 +14170,16 @@
       <c r="F140" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G140" s="26" t="s">
+      <c r="G140" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H140" s="26" t="s">
+      <c r="H140" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I140" s="26" t="s">
+      <c r="I140" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J140" s="26">
+      <c r="J140" s="39">
         <v>6</v>
       </c>
       <c r="K140" s="26" t="s">
@@ -14260,13 +14256,13 @@
       <c r="G141" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="H141" s="26" t="s">
+      <c r="H141" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I141" s="26" t="s">
+      <c r="I141" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J141" s="26">
+      <c r="J141" s="39">
         <v>6</v>
       </c>
       <c r="K141" s="26" t="s">
@@ -14340,16 +14336,16 @@
       <c r="F142" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G142" s="26" t="s">
+      <c r="G142" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H142" s="26" t="s">
+      <c r="H142" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I142" s="26" t="s">
+      <c r="I142" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J142" s="26">
+      <c r="J142" s="39">
         <v>6</v>
       </c>
       <c r="K142" s="26" t="s">
@@ -14426,13 +14422,13 @@
       <c r="G143" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="H143" s="26" t="s">
+      <c r="H143" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I143" s="26" t="s">
+      <c r="I143" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J143" s="26">
+      <c r="J143" s="39">
         <v>6</v>
       </c>
       <c r="K143" s="26" t="s">
@@ -14509,13 +14505,13 @@
       <c r="G144" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="H144" s="26" t="s">
+      <c r="H144" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I144" s="26" t="s">
+      <c r="I144" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J144" s="26">
+      <c r="J144" s="39">
         <v>68</v>
       </c>
       <c r="K144" s="26" t="s">
@@ -14592,13 +14588,13 @@
       <c r="G145" s="39" t="s">
         <v>458</v>
       </c>
-      <c r="H145" s="26" t="s">
+      <c r="H145" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I145" s="26" t="s">
+      <c r="I145" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="J145" s="26">
+      <c r="J145" s="39">
         <v>68</v>
       </c>
       <c r="K145" s="26" t="s">
@@ -14675,13 +14671,13 @@
       <c r="G146" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="H146" s="26" t="s">
+      <c r="H146" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I146" s="26" t="s">
+      <c r="I146" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J146" s="26">
+      <c r="J146" s="39">
         <v>68</v>
       </c>
       <c r="K146" s="26" t="s">
@@ -14755,16 +14751,16 @@
       <c r="F147" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G147" s="26" t="s">
+      <c r="G147" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H147" s="26" t="s">
+      <c r="H147" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I147" s="26" t="s">
+      <c r="I147" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J147" s="26">
+      <c r="J147" s="39">
         <v>68</v>
       </c>
       <c r="K147" s="26" t="s">
@@ -14841,13 +14837,13 @@
       <c r="G148" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="H148" s="26" t="s">
+      <c r="H148" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I148" s="26" t="s">
+      <c r="I148" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J148" s="26">
+      <c r="J148" s="39">
         <v>68</v>
       </c>
       <c r="K148" s="26" t="s">
@@ -14921,16 +14917,16 @@
       <c r="F149" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G149" s="26" t="s">
+      <c r="G149" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H149" s="26" t="s">
+      <c r="H149" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I149" s="26" t="s">
+      <c r="I149" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J149" s="26">
+      <c r="J149" s="39">
         <v>68</v>
       </c>
       <c r="K149" s="26" t="s">
@@ -15007,13 +15003,13 @@
       <c r="G150" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="H150" s="26" t="s">
+      <c r="H150" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I150" s="26" t="s">
+      <c r="I150" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J150" s="26">
+      <c r="J150" s="39">
         <v>68</v>
       </c>
       <c r="K150" s="26" t="s">
@@ -15087,16 +15083,16 @@
       <c r="F151" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G151" s="26" t="s">
+      <c r="G151" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="H151" s="26" t="s">
+      <c r="H151" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I151" s="26" t="s">
+      <c r="I151" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J151" s="26">
+      <c r="J151" s="39">
         <v>16</v>
       </c>
       <c r="K151" s="26" t="s">
@@ -15170,16 +15166,16 @@
       <c r="F152" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G152" s="26" t="s">
+      <c r="G152" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H152" s="26" t="s">
+      <c r="H152" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I152" s="26" t="s">
+      <c r="I152" s="39" t="s">
         <v>345</v>
       </c>
-      <c r="J152" s="26">
+      <c r="J152" s="39">
         <v>16</v>
       </c>
       <c r="K152" s="26" t="s">
@@ -15253,16 +15249,16 @@
       <c r="F153" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G153" s="26" t="s">
+      <c r="G153" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="H153" s="26" t="s">
+      <c r="H153" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I153" s="26" t="s">
+      <c r="I153" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J153" s="26">
+      <c r="J153" s="39">
         <v>16</v>
       </c>
       <c r="K153" s="26" t="s">
@@ -15336,16 +15332,16 @@
       <c r="F154" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G154" s="26" t="s">
+      <c r="G154" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="H154" s="26" t="s">
+      <c r="H154" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I154" s="26" t="s">
+      <c r="I154" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J154" s="26">
+      <c r="J154" s="39">
         <v>36</v>
       </c>
       <c r="K154" s="26" t="s">
@@ -15419,16 +15415,16 @@
       <c r="F155" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G155" s="26" t="s">
+      <c r="G155" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H155" s="26" t="s">
+      <c r="H155" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I155" s="26" t="s">
+      <c r="I155" s="39" t="s">
         <v>345</v>
       </c>
-      <c r="J155" s="26">
+      <c r="J155" s="39">
         <v>36</v>
       </c>
       <c r="K155" s="26" t="s">
@@ -15502,16 +15498,16 @@
       <c r="F156" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G156" s="26" t="s">
+      <c r="G156" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="H156" s="26" t="s">
+      <c r="H156" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I156" s="26" t="s">
+      <c r="I156" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J156" s="26">
+      <c r="J156" s="39">
         <v>36</v>
       </c>
       <c r="K156" s="26" t="s">
@@ -15585,16 +15581,16 @@
       <c r="F157" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G157" s="26" t="s">
+      <c r="G157" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H157" s="26" t="s">
+      <c r="H157" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I157" s="26" t="s">
+      <c r="I157" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J157" s="26">
+      <c r="J157" s="39">
         <v>4</v>
       </c>
       <c r="K157" s="26" t="s">
@@ -15662,16 +15658,16 @@
       <c r="F158" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G158" s="26" t="s">
+      <c r="G158" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="H158" s="26" t="s">
+      <c r="H158" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I158" s="26" t="s">
+      <c r="I158" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J158" s="26">
+      <c r="J158" s="39">
         <v>4</v>
       </c>
       <c r="K158" s="26" t="s">
@@ -15745,16 +15741,16 @@
       <c r="F159" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G159" s="26" t="s">
+      <c r="G159" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="H159" s="26" t="s">
+      <c r="H159" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I159" s="26" t="s">
+      <c r="I159" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J159" s="26">
+      <c r="J159" s="39">
         <v>4</v>
       </c>
       <c r="K159" s="26" t="s">
@@ -15828,16 +15824,16 @@
       <c r="F160" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G160" s="26" t="s">
+      <c r="G160" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H160" s="26" t="s">
+      <c r="H160" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I160" s="26" t="s">
+      <c r="I160" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J160" s="26">
+      <c r="J160" s="39">
         <v>4</v>
       </c>
       <c r="K160" s="26" t="s">
@@ -15911,16 +15907,16 @@
       <c r="F161" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G161" s="26" t="s">
+      <c r="G161" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H161" s="26" t="s">
+      <c r="H161" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I161" s="26" t="s">
+      <c r="I161" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J161" s="26">
+      <c r="J161" s="39">
         <v>4</v>
       </c>
       <c r="K161" s="26" t="s">
@@ -15994,16 +15990,16 @@
       <c r="F162" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G162" s="26" t="s">
+      <c r="G162" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H162" s="26" t="s">
+      <c r="H162" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I162" s="26" t="s">
+      <c r="I162" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J162" s="26">
+      <c r="J162" s="39">
         <v>4</v>
       </c>
       <c r="K162" s="26" t="s">
@@ -16077,16 +16073,16 @@
       <c r="F163" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G163" s="26" t="s">
+      <c r="G163" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H163" s="26" t="s">
+      <c r="H163" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I163" s="26" t="s">
+      <c r="I163" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J163" s="26">
+      <c r="J163" s="39">
         <v>4</v>
       </c>
       <c r="K163" s="26" t="s">
@@ -16160,16 +16156,16 @@
       <c r="F164" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G164" s="26" t="s">
+      <c r="G164" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H164" s="26" t="s">
+      <c r="H164" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I164" s="26" t="s">
+      <c r="I164" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J164" s="26">
+      <c r="J164" s="39">
         <v>4</v>
       </c>
       <c r="K164" s="26" t="s">
@@ -16243,16 +16239,16 @@
       <c r="F165" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G165" s="26" t="s">
+      <c r="G165" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H165" s="26" t="s">
+      <c r="H165" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I165" s="26" t="s">
+      <c r="I165" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J165" s="26">
+      <c r="J165" s="39">
         <v>4</v>
       </c>
       <c r="K165" s="26" t="s">
@@ -16326,16 +16322,16 @@
       <c r="F166" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G166" s="26" t="s">
+      <c r="G166" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H166" s="26" t="s">
+      <c r="H166" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I166" s="26" t="s">
+      <c r="I166" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J166" s="26">
+      <c r="J166" s="39">
         <v>4</v>
       </c>
       <c r="K166" s="26" t="s">
@@ -16409,16 +16405,16 @@
       <c r="F167" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G167" s="26" t="s">
+      <c r="G167" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H167" s="26" t="s">
+      <c r="H167" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I167" s="26" t="s">
+      <c r="I167" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J167" s="26">
+      <c r="J167" s="39">
         <v>4</v>
       </c>
       <c r="K167" s="26" t="s">
@@ -16492,16 +16488,16 @@
       <c r="F168" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G168" s="26" t="s">
+      <c r="G168" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H168" s="26" t="s">
+      <c r="H168" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I168" s="26" t="s">
+      <c r="I168" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J168" s="26">
+      <c r="J168" s="39">
         <v>4</v>
       </c>
       <c r="K168" s="26" t="s">
@@ -16581,16 +16577,16 @@
       <c r="F169" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G169" s="26" t="s">
+      <c r="G169" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="H169" s="26" t="s">
+      <c r="H169" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I169" s="26" t="s">
+      <c r="I169" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J169" s="26">
+      <c r="J169" s="39">
         <v>4</v>
       </c>
       <c r="K169" s="26" t="s">
@@ -16664,16 +16660,16 @@
       <c r="F170" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G170" s="26" t="s">
+      <c r="G170" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H170" s="26" t="s">
+      <c r="H170" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I170" s="26" t="s">
+      <c r="I170" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J170" s="26">
+      <c r="J170" s="39">
         <v>4</v>
       </c>
       <c r="K170" s="26" t="s">
@@ -16753,16 +16749,16 @@
       <c r="F171" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G171" s="26" t="s">
+      <c r="G171" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="H171" s="26" t="s">
+      <c r="H171" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I171" s="26" t="s">
+      <c r="I171" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J171" s="26">
+      <c r="J171" s="39">
         <v>4</v>
       </c>
       <c r="K171" s="26" t="s">
@@ -16842,16 +16838,16 @@
       <c r="F172" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G172" s="26" t="s">
+      <c r="G172" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="H172" s="26" t="s">
+      <c r="H172" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I172" s="26" t="s">
+      <c r="I172" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J172" s="26">
+      <c r="J172" s="39">
         <v>4</v>
       </c>
       <c r="K172" s="26" t="s">
@@ -16931,16 +16927,16 @@
       <c r="F173" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G173" s="26" t="s">
+      <c r="G173" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H173" s="26" t="s">
+      <c r="H173" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I173" s="26" t="s">
+      <c r="I173" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J173" s="26">
+      <c r="J173" s="39">
         <v>4</v>
       </c>
       <c r="K173" s="26" t="s">
@@ -17020,16 +17016,16 @@
       <c r="F174" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G174" s="26" t="s">
+      <c r="G174" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H174" s="26" t="s">
+      <c r="H174" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I174" s="26" t="s">
+      <c r="I174" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J174" s="26">
+      <c r="J174" s="39">
         <v>4</v>
       </c>
       <c r="K174" s="26" t="s">
@@ -17109,16 +17105,16 @@
       <c r="F175" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G175" s="26" t="s">
+      <c r="G175" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H175" s="26" t="s">
+      <c r="H175" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I175" s="26" t="s">
+      <c r="I175" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J175" s="26">
+      <c r="J175" s="39">
         <v>4</v>
       </c>
       <c r="K175" s="26" t="s">
@@ -17198,16 +17194,16 @@
       <c r="F176" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G176" s="26" t="s">
+      <c r="G176" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H176" s="26" t="s">
+      <c r="H176" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I176" s="26" t="s">
+      <c r="I176" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J176" s="26">
+      <c r="J176" s="39">
         <v>4</v>
       </c>
       <c r="K176" s="26" t="s">
@@ -17287,16 +17283,16 @@
       <c r="F177" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G177" s="26" t="s">
+      <c r="G177" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H177" s="26" t="s">
+      <c r="H177" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I177" s="26" t="s">
+      <c r="I177" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J177" s="26">
+      <c r="J177" s="39">
         <v>4</v>
       </c>
       <c r="K177" s="26" t="s">
@@ -17376,16 +17372,16 @@
       <c r="F178" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G178" s="26" t="s">
+      <c r="G178" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H178" s="26" t="s">
+      <c r="H178" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I178" s="26" t="s">
+      <c r="I178" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J178" s="26">
+      <c r="J178" s="39">
         <v>4</v>
       </c>
       <c r="K178" s="26" t="s">
@@ -17465,16 +17461,16 @@
       <c r="F179" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G179" s="26" t="s">
+      <c r="G179" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H179" s="26" t="s">
+      <c r="H179" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I179" s="26" t="s">
+      <c r="I179" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J179" s="26">
+      <c r="J179" s="39">
         <v>4</v>
       </c>
       <c r="K179" s="26" t="s">
@@ -17554,16 +17550,16 @@
       <c r="F180" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G180" s="26" t="s">
+      <c r="G180" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="H180" s="26" t="s">
+      <c r="H180" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I180" s="26" t="s">
+      <c r="I180" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J180" s="26">
+      <c r="J180" s="39">
         <v>4</v>
       </c>
       <c r="K180" s="26" t="s">
@@ -17637,16 +17633,16 @@
       <c r="F181" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G181" s="26" t="s">
+      <c r="G181" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H181" s="26" t="s">
+      <c r="H181" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I181" s="26" t="s">
+      <c r="I181" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J181" s="26">
+      <c r="J181" s="39">
         <v>4</v>
       </c>
       <c r="K181" s="26" t="s">
@@ -17726,16 +17722,16 @@
       <c r="F182" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G182" s="26" t="s">
+      <c r="G182" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="H182" s="26" t="s">
+      <c r="H182" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I182" s="26" t="s">
+      <c r="I182" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J182" s="26">
+      <c r="J182" s="39">
         <v>4</v>
       </c>
       <c r="K182" s="26" t="s">
@@ -17815,16 +17811,16 @@
       <c r="F183" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G183" s="26" t="s">
+      <c r="G183" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="H183" s="26" t="s">
+      <c r="H183" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I183" s="26" t="s">
+      <c r="I183" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J183" s="26">
+      <c r="J183" s="39">
         <v>4</v>
       </c>
       <c r="K183" s="26" t="s">
@@ -17904,16 +17900,16 @@
       <c r="F184" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G184" s="26" t="s">
+      <c r="G184" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H184" s="26" t="s">
+      <c r="H184" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I184" s="26" t="s">
+      <c r="I184" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J184" s="26">
+      <c r="J184" s="39">
         <v>4</v>
       </c>
       <c r="K184" s="26" t="s">
@@ -17993,16 +17989,16 @@
       <c r="F185" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G185" s="26" t="s">
+      <c r="G185" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H185" s="26" t="s">
+      <c r="H185" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I185" s="26" t="s">
+      <c r="I185" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J185" s="26">
+      <c r="J185" s="39">
         <v>4</v>
       </c>
       <c r="K185" s="26" t="s">
@@ -18082,16 +18078,16 @@
       <c r="F186" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G186" s="26" t="s">
+      <c r="G186" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H186" s="26" t="s">
+      <c r="H186" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I186" s="26" t="s">
+      <c r="I186" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J186" s="26">
+      <c r="J186" s="39">
         <v>4</v>
       </c>
       <c r="K186" s="26" t="s">
@@ -18171,16 +18167,16 @@
       <c r="F187" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G187" s="26" t="s">
+      <c r="G187" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H187" s="26" t="s">
+      <c r="H187" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I187" s="26" t="s">
+      <c r="I187" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J187" s="26">
+      <c r="J187" s="39">
         <v>4</v>
       </c>
       <c r="K187" s="26" t="s">
@@ -18260,16 +18256,16 @@
       <c r="F188" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G188" s="26" t="s">
+      <c r="G188" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H188" s="26" t="s">
+      <c r="H188" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I188" s="26" t="s">
+      <c r="I188" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J188" s="26">
+      <c r="J188" s="39">
         <v>4</v>
       </c>
       <c r="K188" s="26" t="s">
@@ -18349,16 +18345,16 @@
       <c r="F189" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G189" s="26" t="s">
+      <c r="G189" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H189" s="26" t="s">
+      <c r="H189" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I189" s="26" t="s">
+      <c r="I189" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J189" s="26">
+      <c r="J189" s="39">
         <v>4</v>
       </c>
       <c r="K189" s="26" t="s">
@@ -18438,16 +18434,16 @@
       <c r="F190" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G190" s="26" t="s">
+      <c r="G190" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H190" s="26" t="s">
+      <c r="H190" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I190" s="26" t="s">
+      <c r="I190" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J190" s="26">
+      <c r="J190" s="39">
         <v>4</v>
       </c>
       <c r="K190" s="26" t="s">
@@ -18521,16 +18517,16 @@
       <c r="F191" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G191" s="26" t="s">
+      <c r="G191" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H191" s="26" t="s">
+      <c r="H191" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I191" s="26" t="s">
+      <c r="I191" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J191" s="26">
+      <c r="J191" s="39">
         <v>4</v>
       </c>
       <c r="K191" s="26" t="s">
@@ -18598,16 +18594,16 @@
       <c r="F192" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G192" s="26" t="s">
+      <c r="G192" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H192" s="26" t="s">
+      <c r="H192" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I192" s="26" t="s">
+      <c r="I192" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J192" s="26">
+      <c r="J192" s="39">
         <v>4</v>
       </c>
       <c r="K192" s="26" t="s">
@@ -18681,16 +18677,16 @@
       <c r="F193" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G193" s="26" t="s">
+      <c r="G193" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="H193" s="26" t="s">
+      <c r="H193" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I193" s="26" t="s">
+      <c r="I193" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J193" s="26">
+      <c r="J193" s="39">
         <v>4</v>
       </c>
       <c r="K193" s="26" t="s">
@@ -18764,16 +18760,16 @@
       <c r="F194" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G194" s="26" t="s">
+      <c r="G194" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="H194" s="26" t="s">
+      <c r="H194" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I194" s="26" t="s">
+      <c r="I194" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J194" s="26">
+      <c r="J194" s="39">
         <v>4</v>
       </c>
       <c r="K194" s="26" t="s">
@@ -18847,16 +18843,16 @@
       <c r="F195" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G195" s="26" t="s">
+      <c r="G195" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H195" s="26" t="s">
+      <c r="H195" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I195" s="26" t="s">
+      <c r="I195" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J195" s="26">
+      <c r="J195" s="39">
         <v>4</v>
       </c>
       <c r="K195" s="26" t="s">
@@ -18930,16 +18926,16 @@
       <c r="F196" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G196" s="26" t="s">
+      <c r="G196" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H196" s="26" t="s">
+      <c r="H196" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I196" s="26" t="s">
+      <c r="I196" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J196" s="26">
+      <c r="J196" s="39">
         <v>4</v>
       </c>
       <c r="K196" s="26" t="s">
@@ -19013,16 +19009,16 @@
       <c r="F197" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G197" s="26" t="s">
+      <c r="G197" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H197" s="26" t="s">
+      <c r="H197" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I197" s="26" t="s">
+      <c r="I197" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J197" s="26">
+      <c r="J197" s="39">
         <v>4</v>
       </c>
       <c r="K197" s="26" t="s">
@@ -19096,16 +19092,16 @@
       <c r="F198" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G198" s="26" t="s">
+      <c r="G198" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H198" s="26" t="s">
+      <c r="H198" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I198" s="26" t="s">
+      <c r="I198" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J198" s="26">
+      <c r="J198" s="39">
         <v>4</v>
       </c>
       <c r="K198" s="26" t="s">
@@ -19179,16 +19175,16 @@
       <c r="F199" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G199" s="26" t="s">
+      <c r="G199" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H199" s="26" t="s">
+      <c r="H199" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I199" s="26" t="s">
+      <c r="I199" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J199" s="26">
+      <c r="J199" s="39">
         <v>4</v>
       </c>
       <c r="K199" s="26" t="s">
@@ -19262,16 +19258,16 @@
       <c r="F200" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G200" s="26" t="s">
+      <c r="G200" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H200" s="26" t="s">
+      <c r="H200" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I200" s="26" t="s">
+      <c r="I200" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J200" s="26">
+      <c r="J200" s="39">
         <v>4</v>
       </c>
       <c r="K200" s="26" t="s">
@@ -19345,16 +19341,16 @@
       <c r="F201" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G201" s="26" t="s">
+      <c r="G201" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H201" s="26" t="s">
+      <c r="H201" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I201" s="26" t="s">
+      <c r="I201" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J201" s="26">
+      <c r="J201" s="39">
         <v>4</v>
       </c>
       <c r="K201" s="26" t="s">
@@ -19428,16 +19424,16 @@
       <c r="F202" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G202" s="26" t="s">
+      <c r="G202" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H202" s="26" t="s">
+      <c r="H202" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I202" s="26" t="s">
+      <c r="I202" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J202" s="26">
+      <c r="J202" s="39">
         <v>12</v>
       </c>
       <c r="K202" s="26" t="s">
@@ -19508,16 +19504,16 @@
       <c r="F203" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G203" s="26" t="s">
+      <c r="G203" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="H203" s="26" t="s">
+      <c r="H203" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I203" s="26" t="s">
+      <c r="I203" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J203" s="26">
+      <c r="J203" s="39">
         <v>12</v>
       </c>
       <c r="K203" s="26" t="s">
@@ -19594,16 +19590,16 @@
       <c r="F204" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G204" s="26" t="s">
+      <c r="G204" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="H204" s="26" t="s">
+      <c r="H204" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I204" s="26" t="s">
+      <c r="I204" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J204" s="26">
+      <c r="J204" s="39">
         <v>12</v>
       </c>
       <c r="K204" s="26" t="s">
@@ -19680,16 +19676,16 @@
       <c r="F205" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G205" s="26" t="s">
+      <c r="G205" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H205" s="26" t="s">
+      <c r="H205" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I205" s="26" t="s">
+      <c r="I205" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J205" s="26">
+      <c r="J205" s="39">
         <v>12</v>
       </c>
       <c r="K205" s="26" t="s">
@@ -19766,16 +19762,16 @@
       <c r="F206" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G206" s="26" t="s">
+      <c r="G206" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H206" s="26" t="s">
+      <c r="H206" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I206" s="26" t="s">
+      <c r="I206" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J206" s="26">
+      <c r="J206" s="39">
         <v>12</v>
       </c>
       <c r="K206" s="26" t="s">
@@ -19852,16 +19848,16 @@
       <c r="F207" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G207" s="26" t="s">
+      <c r="G207" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="H207" s="26" t="s">
+      <c r="H207" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I207" s="26" t="s">
+      <c r="I207" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J207" s="26">
+      <c r="J207" s="39">
         <v>12</v>
       </c>
       <c r="K207" s="26" t="s">
@@ -19938,16 +19934,16 @@
       <c r="F208" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G208" s="26" t="s">
+      <c r="G208" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="H208" s="26" t="s">
+      <c r="H208" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I208" s="26" t="s">
+      <c r="I208" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J208" s="26">
+      <c r="J208" s="39">
         <v>12</v>
       </c>
       <c r="K208" s="26" t="s">
@@ -20024,16 +20020,16 @@
       <c r="F209" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G209" s="26" t="s">
+      <c r="G209" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="H209" s="26" t="s">
+      <c r="H209" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I209" s="26" t="s">
+      <c r="I209" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J209" s="26">
+      <c r="J209" s="39">
         <v>12</v>
       </c>
       <c r="K209" s="26" t="s">
@@ -20110,16 +20106,16 @@
       <c r="F210" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G210" s="26" t="s">
+      <c r="G210" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H210" s="26" t="s">
+      <c r="H210" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I210" s="26" t="s">
+      <c r="I210" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J210" s="26">
+      <c r="J210" s="39">
         <v>4</v>
       </c>
       <c r="K210" s="26" t="s">
@@ -20187,16 +20183,16 @@
       <c r="F211" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G211" s="26" t="s">
+      <c r="G211" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H211" s="26" t="s">
+      <c r="H211" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I211" s="26" t="s">
+      <c r="I211" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J211" s="26">
+      <c r="J211" s="39">
         <v>4</v>
       </c>
       <c r="K211" s="26" t="s">
@@ -20270,16 +20266,16 @@
       <c r="F212" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G212" s="26" t="s">
+      <c r="G212" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H212" s="26" t="s">
+      <c r="H212" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I212" s="26" t="s">
+      <c r="I212" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J212" s="26">
+      <c r="J212" s="39">
         <v>4</v>
       </c>
       <c r="K212" s="26" t="s">
@@ -20353,16 +20349,16 @@
       <c r="F213" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G213" s="26" t="s">
+      <c r="G213" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H213" s="26" t="s">
+      <c r="H213" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I213" s="26" t="s">
+      <c r="I213" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J213" s="26">
+      <c r="J213" s="39">
         <v>4</v>
       </c>
       <c r="K213" s="26" t="s">
@@ -20436,16 +20432,16 @@
       <c r="F214" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G214" s="26" t="s">
+      <c r="G214" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H214" s="26" t="s">
+      <c r="H214" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I214" s="26" t="s">
+      <c r="I214" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J214" s="26">
+      <c r="J214" s="39">
         <v>4</v>
       </c>
       <c r="K214" s="26" t="s">
@@ -20519,16 +20515,16 @@
       <c r="F215" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G215" s="26" t="s">
+      <c r="G215" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H215" s="26" t="s">
+      <c r="H215" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I215" s="26" t="s">
+      <c r="I215" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J215" s="26">
+      <c r="J215" s="39">
         <v>4</v>
       </c>
       <c r="K215" s="26" t="s">
@@ -20602,16 +20598,16 @@
       <c r="F216" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G216" s="26" t="s">
+      <c r="G216" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H216" s="26" t="s">
+      <c r="H216" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I216" s="26" t="s">
+      <c r="I216" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J216" s="26">
+      <c r="J216" s="39">
         <v>4</v>
       </c>
       <c r="K216" s="26" t="s">
@@ -20688,13 +20684,13 @@
       <c r="G217" s="39" t="s">
         <v>459</v>
       </c>
-      <c r="H217" s="26" t="s">
+      <c r="H217" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I217" s="26" t="s">
+      <c r="I217" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J217" s="26">
+      <c r="J217" s="39">
         <v>4</v>
       </c>
       <c r="K217" s="26" t="s">
@@ -20768,16 +20764,16 @@
       <c r="F218" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G218" s="26" t="s">
+      <c r="G218" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H218" s="26" t="s">
+      <c r="H218" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I218" s="26" t="s">
+      <c r="I218" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J218" s="26">
+      <c r="J218" s="39">
         <v>4</v>
       </c>
       <c r="K218" s="26" t="s">
@@ -20851,16 +20847,16 @@
       <c r="F219" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G219" s="26" t="s">
+      <c r="G219" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H219" s="26" t="s">
+      <c r="H219" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I219" s="26" t="s">
+      <c r="I219" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J219" s="26">
+      <c r="J219" s="39">
         <v>4</v>
       </c>
       <c r="K219" s="26" t="s">
@@ -20934,16 +20930,16 @@
       <c r="F220" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G220" s="26" t="s">
+      <c r="G220" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H220" s="26" t="s">
+      <c r="H220" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I220" s="26" t="s">
+      <c r="I220" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J220" s="26">
+      <c r="J220" s="39">
         <v>4</v>
       </c>
       <c r="K220" s="26" t="s">
@@ -21017,16 +21013,16 @@
       <c r="F221" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G221" s="26" t="s">
+      <c r="G221" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H221" s="26" t="s">
+      <c r="H221" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I221" s="26" t="s">
+      <c r="I221" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J221" s="26">
+      <c r="J221" s="39">
         <v>8</v>
       </c>
       <c r="K221" s="26" t="s">
@@ -21100,16 +21096,16 @@
       <c r="F222" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G222" s="26" t="s">
+      <c r="G222" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H222" s="26" t="s">
+      <c r="H222" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I222" s="26" t="s">
+      <c r="I222" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J222" s="26">
+      <c r="J222" s="39">
         <v>8</v>
       </c>
       <c r="K222" s="26" t="s">
@@ -21183,16 +21179,16 @@
       <c r="F223" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G223" s="26" t="s">
+      <c r="G223" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H223" s="26" t="s">
+      <c r="H223" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I223" s="26" t="s">
+      <c r="I223" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J223" s="26">
+      <c r="J223" s="39">
         <v>8</v>
       </c>
       <c r="K223" s="26" t="s">
@@ -21266,16 +21262,16 @@
       <c r="F224" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G224" s="26" t="s">
+      <c r="G224" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H224" s="26" t="s">
+      <c r="H224" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I224" s="26" t="s">
+      <c r="I224" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J224" s="26">
+      <c r="J224" s="39">
         <v>8</v>
       </c>
       <c r="K224" s="26" t="s">
@@ -21349,16 +21345,16 @@
       <c r="F225" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G225" s="26" t="s">
+      <c r="G225" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H225" s="26" t="s">
+      <c r="H225" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I225" s="26" t="s">
+      <c r="I225" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J225" s="26">
+      <c r="J225" s="39">
         <v>8</v>
       </c>
       <c r="K225" s="26" t="s">
@@ -21432,16 +21428,16 @@
       <c r="F226" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G226" s="26" t="s">
+      <c r="G226" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H226" s="26" t="s">
+      <c r="H226" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I226" s="26" t="s">
+      <c r="I226" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J226" s="26">
+      <c r="J226" s="39">
         <v>8</v>
       </c>
       <c r="K226" s="26" t="s">
@@ -21518,13 +21514,13 @@
       <c r="G227" s="39" t="s">
         <v>459</v>
       </c>
-      <c r="H227" s="26" t="s">
+      <c r="H227" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I227" s="26" t="s">
+      <c r="I227" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J227" s="26">
+      <c r="J227" s="39">
         <v>8</v>
       </c>
       <c r="K227" s="26" t="s">
@@ -21598,16 +21594,16 @@
       <c r="F228" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G228" s="26" t="s">
+      <c r="G228" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H228" s="26" t="s">
+      <c r="H228" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I228" s="26" t="s">
+      <c r="I228" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J228" s="26">
+      <c r="J228" s="39">
         <v>8</v>
       </c>
       <c r="K228" s="26" t="s">
@@ -21681,16 +21677,16 @@
       <c r="F229" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G229" s="26" t="s">
+      <c r="G229" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H229" s="26" t="s">
+      <c r="H229" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I229" s="26" t="s">
+      <c r="I229" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J229" s="26">
+      <c r="J229" s="39">
         <v>8</v>
       </c>
       <c r="K229" s="26" t="s">
@@ -21764,16 +21760,16 @@
       <c r="F230" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G230" s="26" t="s">
+      <c r="G230" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H230" s="26" t="s">
+      <c r="H230" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I230" s="26" t="s">
+      <c r="I230" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J230" s="26">
+      <c r="J230" s="39">
         <v>8</v>
       </c>
       <c r="K230" s="26" t="s">
@@ -21847,16 +21843,16 @@
       <c r="F231" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G231" s="26" t="s">
+      <c r="G231" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="H231" s="26" t="s">
+      <c r="H231" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I231" s="26" t="s">
+      <c r="I231" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="J231" s="26">
+      <c r="J231" s="39">
         <v>2</v>
       </c>
       <c r="K231" s="26" t="s">
@@ -21930,16 +21926,16 @@
       <c r="F232" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G232" s="26" t="s">
+      <c r="G232" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="H232" s="26" t="s">
+      <c r="H232" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I232" s="26" t="s">
+      <c r="I232" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J232" s="26">
+      <c r="J232" s="39">
         <v>2</v>
       </c>
       <c r="K232" s="26" t="s">
@@ -22013,16 +22009,16 @@
       <c r="F233" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G233" s="26" t="s">
+      <c r="G233" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="H233" s="26" t="s">
+      <c r="H233" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I233" s="26" t="s">
+      <c r="I233" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J233" s="26">
+      <c r="J233" s="39">
         <v>2</v>
       </c>
       <c r="K233" s="26" t="s">
@@ -22096,16 +22092,16 @@
       <c r="F234" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G234" s="26" t="s">
+      <c r="G234" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="H234" s="26" t="s">
+      <c r="H234" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I234" s="26" t="s">
+      <c r="I234" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J234" s="26">
+      <c r="J234" s="39">
         <v>2</v>
       </c>
       <c r="K234" s="26" t="s">
@@ -22179,16 +22175,16 @@
       <c r="F235" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G235" s="26" t="s">
+      <c r="G235" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H235" s="26" t="s">
+      <c r="H235" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I235" s="26" t="s">
+      <c r="I235" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J235" s="26">
+      <c r="J235" s="39">
         <v>4</v>
       </c>
       <c r="K235" s="26" t="s">
@@ -22262,16 +22258,16 @@
       <c r="F236" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G236" s="26" t="s">
+      <c r="G236" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="H236" s="26" t="s">
+      <c r="H236" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I236" s="26" t="s">
+      <c r="I236" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J236" s="26">
+      <c r="J236" s="39">
         <v>4</v>
       </c>
       <c r="K236" s="26" t="s">
@@ -22345,16 +22341,16 @@
       <c r="F237" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G237" s="26" t="s">
+      <c r="G237" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="H237" s="26" t="s">
+      <c r="H237" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I237" s="26" t="s">
+      <c r="I237" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J237" s="26">
+      <c r="J237" s="39">
         <v>4</v>
       </c>
       <c r="K237" s="26" t="s">
@@ -22428,16 +22424,16 @@
       <c r="F238" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G238" s="26" t="s">
+      <c r="G238" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="H238" s="26" t="s">
+      <c r="H238" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I238" s="26" t="s">
+      <c r="I238" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J238" s="26">
+      <c r="J238" s="39">
         <v>12</v>
       </c>
       <c r="K238" s="26" t="s">
@@ -22514,16 +22510,16 @@
       <c r="F239" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G239" s="26" t="s">
+      <c r="G239" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H239" s="26" t="s">
+      <c r="H239" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I239" s="26" t="s">
+      <c r="I239" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J239" s="26">
+      <c r="J239" s="39">
         <v>12</v>
       </c>
       <c r="K239" s="26" t="s">
@@ -22600,16 +22596,16 @@
       <c r="F240" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G240" s="26" t="s">
+      <c r="G240" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H240" s="26" t="s">
+      <c r="H240" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I240" s="26" t="s">
+      <c r="I240" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J240" s="26">
+      <c r="J240" s="39">
         <v>12</v>
       </c>
       <c r="K240" s="26" t="s">
@@ -22686,16 +22682,16 @@
       <c r="F241" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G241" s="26" t="s">
+      <c r="G241" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H241" s="26" t="s">
+      <c r="H241" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I241" s="26" t="s">
+      <c r="I241" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J241" s="26">
+      <c r="J241" s="39">
         <v>12</v>
       </c>
       <c r="K241" s="26" t="s">
@@ -22772,16 +22768,16 @@
       <c r="F242" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G242" s="26" t="s">
+      <c r="G242" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H242" s="26" t="s">
+      <c r="H242" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I242" s="26" t="s">
+      <c r="I242" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J242" s="26">
+      <c r="J242" s="39">
         <v>12</v>
       </c>
       <c r="K242" s="26" t="s">
@@ -22858,16 +22854,16 @@
       <c r="F243" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G243" s="26" t="s">
+      <c r="G243" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H243" s="26" t="s">
+      <c r="H243" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I243" s="26" t="s">
+      <c r="I243" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J243" s="26">
+      <c r="J243" s="39">
         <v>12</v>
       </c>
       <c r="K243" s="26" t="s">
@@ -22944,16 +22940,16 @@
       <c r="F244" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G244" s="26" t="s">
+      <c r="G244" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="H244" s="26" t="s">
+      <c r="H244" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I244" s="26" t="s">
+      <c r="I244" s="39" t="s">
         <v>373</v>
       </c>
-      <c r="J244" s="26">
+      <c r="J244" s="39">
         <v>12</v>
       </c>
       <c r="K244" s="26" t="s">
@@ -23036,16 +23032,16 @@
       <c r="F245" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G245" s="26" t="s">
+      <c r="G245" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H245" s="26" t="s">
+      <c r="H245" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I245" s="26" t="s">
+      <c r="I245" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J245" s="26">
+      <c r="J245" s="39">
         <v>8</v>
       </c>
       <c r="K245" s="26" t="s">
@@ -23125,16 +23121,16 @@
       <c r="F246" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G246" s="26" t="s">
+      <c r="G246" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="H246" s="26" t="s">
+      <c r="H246" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I246" s="26" t="s">
+      <c r="I246" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J246" s="26">
+      <c r="J246" s="39">
         <v>8</v>
       </c>
       <c r="K246" s="26" t="s">
@@ -23214,16 +23210,16 @@
       <c r="F247" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G247" s="26" t="s">
+      <c r="G247" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H247" s="26" t="s">
+      <c r="H247" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I247" s="26" t="s">
+      <c r="I247" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J247" s="26">
+      <c r="J247" s="39">
         <v>8</v>
       </c>
       <c r="K247" s="26" t="s">
@@ -23303,16 +23299,16 @@
       <c r="F248" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G248" s="26" t="s">
+      <c r="G248" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H248" s="26" t="s">
+      <c r="H248" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I248" s="26" t="s">
+      <c r="I248" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J248" s="26">
+      <c r="J248" s="39">
         <v>8</v>
       </c>
       <c r="K248" s="26" t="s">
@@ -23392,16 +23388,16 @@
       <c r="F249" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G249" s="26" t="s">
+      <c r="G249" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="H249" s="26" t="s">
+      <c r="H249" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I249" s="26" t="s">
+      <c r="I249" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J249" s="26">
+      <c r="J249" s="39">
         <v>8</v>
       </c>
       <c r="K249" s="26" t="s">
@@ -23481,16 +23477,16 @@
       <c r="F250" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G250" s="26" t="s">
+      <c r="G250" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="H250" s="26" t="s">
+      <c r="H250" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I250" s="26" t="s">
+      <c r="I250" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J250" s="26">
+      <c r="J250" s="39">
         <v>8</v>
       </c>
       <c r="K250" s="26" t="s">
@@ -23570,16 +23566,16 @@
       <c r="F251" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G251" s="26" t="s">
+      <c r="G251" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H251" s="26" t="s">
+      <c r="H251" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I251" s="26" t="s">
+      <c r="I251" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J251" s="26">
+      <c r="J251" s="39">
         <v>8</v>
       </c>
       <c r="K251" s="26" t="s">
@@ -23659,16 +23655,16 @@
       <c r="F252" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G252" s="26" t="s">
+      <c r="G252" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H252" s="26" t="s">
+      <c r="H252" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I252" s="26" t="s">
+      <c r="I252" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="J252" s="26">
+      <c r="J252" s="39">
         <v>8</v>
       </c>
       <c r="K252" s="26" t="s">
@@ -23748,16 +23744,16 @@
       <c r="F253" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G253" s="26" t="s">
+      <c r="G253" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H253" s="26" t="s">
+      <c r="H253" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I253" s="26" t="s">
+      <c r="I253" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J253" s="26">
+      <c r="J253" s="39">
         <v>20</v>
       </c>
       <c r="K253" s="26" t="s">
@@ -23831,16 +23827,16 @@
       <c r="F254" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G254" s="26" t="s">
+      <c r="G254" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H254" s="26" t="s">
+      <c r="H254" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I254" s="26" t="s">
+      <c r="I254" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J254" s="26">
+      <c r="J254" s="39">
         <v>20</v>
       </c>
       <c r="K254" s="26" t="s">
@@ -23920,16 +23916,16 @@
       <c r="F255" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G255" s="26" t="s">
+      <c r="G255" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H255" s="26" t="s">
+      <c r="H255" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I255" s="26" t="s">
+      <c r="I255" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J255" s="26">
+      <c r="J255" s="39">
         <v>20</v>
       </c>
       <c r="K255" s="26" t="s">
@@ -24009,16 +24005,16 @@
       <c r="F256" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G256" s="26" t="s">
+      <c r="G256" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H256" s="26" t="s">
+      <c r="H256" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I256" s="26" t="s">
+      <c r="I256" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J256" s="26">
+      <c r="J256" s="39">
         <v>20</v>
       </c>
       <c r="K256" s="26" t="s">
@@ -24092,16 +24088,16 @@
       <c r="F257" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G257" s="26" t="s">
+      <c r="G257" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H257" s="26" t="s">
+      <c r="H257" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I257" s="26" t="s">
+      <c r="I257" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J257" s="26">
+      <c r="J257" s="39">
         <v>20</v>
       </c>
       <c r="K257" s="26" t="s">
@@ -24181,16 +24177,16 @@
       <c r="F258" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G258" s="26" t="s">
+      <c r="G258" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H258" s="26" t="s">
+      <c r="H258" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I258" s="26" t="s">
+      <c r="I258" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J258" s="26">
+      <c r="J258" s="39">
         <v>20</v>
       </c>
       <c r="K258" s="26" t="s">
@@ -24270,16 +24266,16 @@
       <c r="F259" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G259" s="26" t="s">
+      <c r="G259" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H259" s="26" t="s">
+      <c r="H259" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I259" s="26" t="s">
+      <c r="I259" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J259" s="26">
+      <c r="J259" s="39">
         <v>52</v>
       </c>
       <c r="K259" s="26" t="s">
@@ -24353,16 +24349,16 @@
       <c r="F260" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G260" s="26" t="s">
+      <c r="G260" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H260" s="26" t="s">
+      <c r="H260" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I260" s="26" t="s">
+      <c r="I260" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J260" s="26">
+      <c r="J260" s="39">
         <v>52</v>
       </c>
       <c r="K260" s="26" t="s">
@@ -24442,16 +24438,16 @@
       <c r="F261" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G261" s="26" t="s">
+      <c r="G261" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H261" s="26" t="s">
+      <c r="H261" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I261" s="26" t="s">
+      <c r="I261" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J261" s="26">
+      <c r="J261" s="39">
         <v>52</v>
       </c>
       <c r="K261" s="26" t="s">
@@ -24525,16 +24521,16 @@
       <c r="F262" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G262" s="26" t="s">
+      <c r="G262" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="H262" s="26" t="s">
+      <c r="H262" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I262" s="26" t="s">
+      <c r="I262" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J262" s="26">
+      <c r="J262" s="39">
         <v>10</v>
       </c>
       <c r="K262" s="26" t="s">
@@ -24608,16 +24604,16 @@
       <c r="F263" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G263" s="26" t="s">
+      <c r="G263" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H263" s="26" t="s">
+      <c r="H263" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I263" s="26" t="s">
+      <c r="I263" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J263" s="26">
+      <c r="J263" s="39">
         <v>10</v>
       </c>
       <c r="K263" s="26" t="s">
@@ -24691,16 +24687,16 @@
       <c r="F264" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G264" s="26" t="s">
+      <c r="G264" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H264" s="26" t="s">
+      <c r="H264" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I264" s="26" t="s">
+      <c r="I264" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J264" s="26">
+      <c r="J264" s="39">
         <v>10</v>
       </c>
       <c r="K264" s="26" t="s">
@@ -24774,16 +24770,16 @@
       <c r="F265" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G265" s="26" t="s">
+      <c r="G265" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H265" s="26" t="s">
+      <c r="H265" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I265" s="26" t="s">
+      <c r="I265" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J265" s="26">
+      <c r="J265" s="39">
         <v>10</v>
       </c>
       <c r="K265" s="26" t="s">
@@ -24857,16 +24853,16 @@
       <c r="F266" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G266" s="26" t="s">
+      <c r="G266" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H266" s="26" t="s">
+      <c r="H266" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I266" s="26" t="s">
+      <c r="I266" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J266" s="26">
+      <c r="J266" s="39">
         <v>10</v>
       </c>
       <c r="K266" s="26" t="s">
@@ -24940,16 +24936,16 @@
       <c r="F267" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G267" s="26" t="s">
+      <c r="G267" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H267" s="26" t="s">
+      <c r="H267" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I267" s="26" t="s">
+      <c r="I267" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J267" s="26">
+      <c r="J267" s="39">
         <v>10</v>
       </c>
       <c r="K267" s="26" t="s">
@@ -25023,16 +25019,16 @@
       <c r="F268" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G268" s="26" t="s">
+      <c r="G268" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H268" s="26" t="s">
+      <c r="H268" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I268" s="26" t="s">
+      <c r="I268" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J268" s="26">
+      <c r="J268" s="39">
         <v>10</v>
       </c>
       <c r="K268" s="26" t="s">
@@ -25106,16 +25102,16 @@
       <c r="F269" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G269" s="26" t="s">
+      <c r="G269" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H269" s="26" t="s">
+      <c r="H269" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I269" s="26" t="s">
+      <c r="I269" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J269" s="26">
+      <c r="J269" s="39">
         <v>10</v>
       </c>
       <c r="K269" s="26" t="s">
@@ -25189,16 +25185,16 @@
       <c r="F270" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G270" s="26" t="s">
+      <c r="G270" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="H270" s="26" t="s">
+      <c r="H270" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I270" s="26" t="s">
+      <c r="I270" s="39" t="s">
         <v>310</v>
       </c>
-      <c r="J270" s="26">
+      <c r="J270" s="39">
         <v>12</v>
       </c>
       <c r="K270" s="26" t="s">
@@ -25272,13 +25268,13 @@
       <c r="G271" s="39" t="s">
         <v>460</v>
       </c>
-      <c r="H271" s="26" t="s">
+      <c r="H271" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I271" s="26" t="s">
+      <c r="I271" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J271" s="26">
+      <c r="J271" s="39">
         <v>12</v>
       </c>
       <c r="K271" s="26" t="s">
@@ -25358,13 +25354,13 @@
       <c r="G272" s="39" t="s">
         <v>461</v>
       </c>
-      <c r="H272" s="26" t="s">
+      <c r="H272" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I272" s="26" t="s">
+      <c r="I272" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J272" s="26">
+      <c r="J272" s="39">
         <v>12</v>
       </c>
       <c r="K272" s="26" t="s">
@@ -25441,16 +25437,16 @@
       <c r="F273" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G273" s="26" t="s">
+      <c r="G273" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="H273" s="26" t="s">
+      <c r="H273" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I273" s="26" t="s">
+      <c r="I273" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J273" s="26">
+      <c r="J273" s="39">
         <v>12</v>
       </c>
       <c r="K273" s="26" t="s">
@@ -25527,16 +25523,16 @@
       <c r="F274" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G274" s="26" t="s">
+      <c r="G274" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="H274" s="26" t="s">
+      <c r="H274" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I274" s="26" t="s">
+      <c r="I274" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J274" s="26">
+      <c r="J274" s="39">
         <v>12</v>
       </c>
       <c r="K274" s="26" t="s">
@@ -25613,16 +25609,16 @@
       <c r="F275" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G275" s="26" t="s">
+      <c r="G275" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H275" s="26" t="s">
+      <c r="H275" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I275" s="26" t="s">
+      <c r="I275" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J275" s="26">
+      <c r="J275" s="39">
         <v>12</v>
       </c>
       <c r="K275" s="26" t="s">
@@ -25699,16 +25695,16 @@
       <c r="F276" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G276" s="26" t="s">
+      <c r="G276" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="H276" s="26" t="s">
+      <c r="H276" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I276" s="26" t="s">
+      <c r="I276" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J276" s="26">
+      <c r="J276" s="39">
         <v>12</v>
       </c>
       <c r="K276" s="26" t="s">
@@ -25785,16 +25781,16 @@
       <c r="F277" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G277" s="26" t="s">
+      <c r="G277" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="H277" s="26" t="s">
+      <c r="H277" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I277" s="26" t="s">
+      <c r="I277" s="39" t="s">
         <v>380</v>
       </c>
-      <c r="J277" s="26">
+      <c r="J277" s="39">
         <v>12</v>
       </c>
       <c r="K277" s="26" t="s">
@@ -25871,16 +25867,16 @@
       <c r="F278" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G278" s="26" t="s">
+      <c r="G278" s="39" t="s">
         <v>383</v>
       </c>
-      <c r="H278" s="26" t="s">
+      <c r="H278" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I278" s="26" t="s">
+      <c r="I278" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J278" s="26">
+      <c r="J278" s="39">
         <v>12</v>
       </c>
       <c r="K278" s="26" t="s">
@@ -25957,16 +25953,16 @@
       <c r="F279" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G279" s="26" t="s">
+      <c r="G279" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="H279" s="26" t="s">
+      <c r="H279" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I279" s="26" t="s">
+      <c r="I279" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J279" s="26">
+      <c r="J279" s="39">
         <v>12</v>
       </c>
       <c r="K279" s="26" t="s">
@@ -26043,16 +26039,16 @@
       <c r="F280" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G280" s="26" t="s">
+      <c r="G280" s="39" t="s">
         <v>384</v>
       </c>
-      <c r="H280" s="26" t="s">
+      <c r="H280" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I280" s="26" t="s">
+      <c r="I280" s="39" t="s">
         <v>381</v>
       </c>
-      <c r="J280" s="26">
+      <c r="J280" s="39">
         <v>12</v>
       </c>
       <c r="K280" s="26" t="s">
@@ -26129,16 +26125,16 @@
       <c r="F281" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G281" s="26" t="s">
+      <c r="G281" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="H281" s="26" t="s">
+      <c r="H281" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I281" s="26" t="s">
+      <c r="I281" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J281" s="26">
+      <c r="J281" s="39">
         <v>12</v>
       </c>
       <c r="K281" s="26" t="s">
@@ -26215,16 +26211,16 @@
       <c r="F282" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G282" s="26" t="s">
+      <c r="G282" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="H282" s="26" t="s">
+      <c r="H282" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I282" s="26" t="s">
+      <c r="I282" s="39" t="s">
         <v>310</v>
       </c>
-      <c r="J282" s="26">
+      <c r="J282" s="39">
         <v>12</v>
       </c>
       <c r="K282" s="26" t="s">
@@ -26295,16 +26291,16 @@
       <c r="F283" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G283" s="26" t="s">
+      <c r="G283" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="H283" s="26" t="s">
+      <c r="H283" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I283" s="26" t="s">
+      <c r="I283" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J283" s="26">
+      <c r="J283" s="39">
         <v>12</v>
       </c>
       <c r="K283" s="26" t="s">
@@ -26381,16 +26377,16 @@
       <c r="F284" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G284" s="26" t="s">
+      <c r="G284" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="H284" s="26" t="s">
+      <c r="H284" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I284" s="26" t="s">
+      <c r="I284" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J284" s="26">
+      <c r="J284" s="39">
         <v>12</v>
       </c>
       <c r="K284" s="26" t="s">
@@ -26467,16 +26463,16 @@
       <c r="F285" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G285" s="26" t="s">
+      <c r="G285" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H285" s="26" t="s">
+      <c r="H285" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I285" s="26" t="s">
+      <c r="I285" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J285" s="26">
+      <c r="J285" s="39">
         <v>12</v>
       </c>
       <c r="K285" s="26" t="s">
@@ -26553,16 +26549,16 @@
       <c r="F286" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G286" s="26" t="s">
+      <c r="G286" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="H286" s="26" t="s">
+      <c r="H286" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I286" s="26" t="s">
+      <c r="I286" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J286" s="26">
+      <c r="J286" s="39">
         <v>12</v>
       </c>
       <c r="K286" s="26" t="s">
@@ -26639,16 +26635,16 @@
       <c r="F287" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G287" s="26" t="s">
+      <c r="G287" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="H287" s="26" t="s">
+      <c r="H287" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I287" s="26" t="s">
+      <c r="I287" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J287" s="26">
+      <c r="J287" s="39">
         <v>12</v>
       </c>
       <c r="K287" s="26" t="s">
@@ -26725,16 +26721,16 @@
       <c r="F288" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G288" s="26" t="s">
+      <c r="G288" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="H288" s="26" t="s">
+      <c r="H288" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I288" s="26" t="s">
+      <c r="I288" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J288" s="26">
+      <c r="J288" s="39">
         <v>12</v>
       </c>
       <c r="K288" s="26" t="s">
@@ -26811,16 +26807,16 @@
       <c r="F289" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G289" s="26" t="s">
+      <c r="G289" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H289" s="26" t="s">
+      <c r="H289" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I289" s="26" t="s">
+      <c r="I289" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J289" s="26">
+      <c r="J289" s="39">
         <v>12</v>
       </c>
       <c r="K289" s="26" t="s">
@@ -26897,16 +26893,16 @@
       <c r="F290" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G290" s="26" t="s">
+      <c r="G290" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H290" s="26" t="s">
+      <c r="H290" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I290" s="26" t="s">
+      <c r="I290" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="J290" s="26">
+      <c r="J290" s="39">
         <v>10</v>
       </c>
       <c r="K290" s="26" t="s">
@@ -26977,16 +26973,16 @@
       <c r="F291" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G291" s="26" t="s">
+      <c r="G291" s="39" t="s">
         <v>391</v>
       </c>
-      <c r="H291" s="26" t="s">
+      <c r="H291" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I291" s="26" t="s">
+      <c r="I291" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J291" s="26">
+      <c r="J291" s="39">
         <v>10</v>
       </c>
       <c r="K291" s="26" t="s">
@@ -27066,13 +27062,13 @@
       <c r="G292" s="39" t="s">
         <v>462</v>
       </c>
-      <c r="H292" s="26" t="s">
+      <c r="H292" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I292" s="26" t="s">
+      <c r="I292" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J292" s="26">
+      <c r="J292" s="39">
         <v>4</v>
       </c>
       <c r="K292" s="26" t="s">
@@ -27152,13 +27148,13 @@
       <c r="G293" s="39" t="s">
         <v>463</v>
       </c>
-      <c r="H293" s="26" t="s">
+      <c r="H293" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I293" s="26" t="s">
+      <c r="I293" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J293" s="26">
+      <c r="J293" s="39">
         <v>4</v>
       </c>
       <c r="K293" s="26" t="s">
@@ -27235,16 +27231,16 @@
       <c r="F294" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G294" s="26" t="s">
+      <c r="G294" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H294" s="26" t="s">
+      <c r="H294" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I294" s="26" t="s">
+      <c r="I294" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J294" s="26">
+      <c r="J294" s="39">
         <v>4</v>
       </c>
       <c r="K294" s="26" t="s">
@@ -27321,16 +27317,16 @@
       <c r="F295" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G295" s="26" t="s">
+      <c r="G295" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H295" s="26" t="s">
+      <c r="H295" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I295" s="26" t="s">
+      <c r="I295" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J295" s="26">
+      <c r="J295" s="39">
         <v>4</v>
       </c>
       <c r="K295" s="26" t="s">
@@ -27407,16 +27403,16 @@
       <c r="F296" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G296" s="26" t="s">
+      <c r="G296" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H296" s="26" t="s">
+      <c r="H296" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I296" s="26" t="s">
+      <c r="I296" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J296" s="26">
+      <c r="J296" s="39">
         <v>4</v>
       </c>
       <c r="K296" s="26" t="s">
@@ -27493,16 +27489,16 @@
       <c r="F297" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G297" s="26" t="s">
+      <c r="G297" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H297" s="26" t="s">
+      <c r="H297" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I297" s="26" t="s">
+      <c r="I297" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J297" s="26">
+      <c r="J297" s="39">
         <v>4</v>
       </c>
       <c r="K297" s="26" t="s">
@@ -27579,16 +27575,16 @@
       <c r="F298" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G298" s="26" t="s">
+      <c r="G298" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H298" s="26" t="s">
+      <c r="H298" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I298" s="26" t="s">
+      <c r="I298" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J298" s="26">
+      <c r="J298" s="39">
         <v>4</v>
       </c>
       <c r="K298" s="26" t="s">
@@ -27665,16 +27661,16 @@
       <c r="F299" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G299" s="26" t="s">
+      <c r="G299" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H299" s="26" t="s">
+      <c r="H299" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I299" s="26" t="s">
+      <c r="I299" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J299" s="26">
+      <c r="J299" s="39">
         <v>4</v>
       </c>
       <c r="K299" s="26" t="s">
@@ -27754,13 +27750,13 @@
       <c r="G300" s="39" t="s">
         <v>462</v>
       </c>
-      <c r="H300" s="26" t="s">
+      <c r="H300" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I300" s="26" t="s">
+      <c r="I300" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J300" s="26">
+      <c r="J300" s="39">
         <v>12</v>
       </c>
       <c r="K300" s="26" t="s">
@@ -27840,13 +27836,13 @@
       <c r="G301" s="39" t="s">
         <v>463</v>
       </c>
-      <c r="H301" s="26" t="s">
+      <c r="H301" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I301" s="26" t="s">
+      <c r="I301" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J301" s="26">
+      <c r="J301" s="39">
         <v>12</v>
       </c>
       <c r="K301" s="26" t="s">
@@ -27923,16 +27919,16 @@
       <c r="F302" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G302" s="26" t="s">
+      <c r="G302" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H302" s="26" t="s">
+      <c r="H302" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I302" s="26" t="s">
+      <c r="I302" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J302" s="26">
+      <c r="J302" s="39">
         <v>12</v>
       </c>
       <c r="K302" s="26" t="s">
@@ -28009,16 +28005,16 @@
       <c r="F303" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G303" s="26" t="s">
+      <c r="G303" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H303" s="26" t="s">
+      <c r="H303" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I303" s="26" t="s">
+      <c r="I303" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J303" s="26">
+      <c r="J303" s="39">
         <v>12</v>
       </c>
       <c r="K303" s="26" t="s">
@@ -28095,16 +28091,16 @@
       <c r="F304" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G304" s="26" t="s">
+      <c r="G304" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H304" s="26" t="s">
+      <c r="H304" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I304" s="26" t="s">
+      <c r="I304" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J304" s="26">
+      <c r="J304" s="39">
         <v>12</v>
       </c>
       <c r="K304" s="26" t="s">
@@ -28181,16 +28177,16 @@
       <c r="F305" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G305" s="26" t="s">
+      <c r="G305" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H305" s="26" t="s">
+      <c r="H305" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I305" s="26" t="s">
+      <c r="I305" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J305" s="26">
+      <c r="J305" s="39">
         <v>12</v>
       </c>
       <c r="K305" s="26" t="s">
@@ -28267,16 +28263,16 @@
       <c r="F306" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G306" s="26" t="s">
+      <c r="G306" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H306" s="26" t="s">
+      <c r="H306" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I306" s="26" t="s">
+      <c r="I306" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J306" s="26">
+      <c r="J306" s="39">
         <v>12</v>
       </c>
       <c r="K306" s="26" t="s">
@@ -28353,16 +28349,16 @@
       <c r="F307" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G307" s="26" t="s">
+      <c r="G307" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H307" s="26" t="s">
+      <c r="H307" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I307" s="26" t="s">
+      <c r="I307" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J307" s="26">
+      <c r="J307" s="39">
         <v>12</v>
       </c>
       <c r="K307" s="26" t="s">
@@ -28439,16 +28435,16 @@
       <c r="F308" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G308" s="26" t="s">
+      <c r="G308" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="H308" s="26" t="s">
+      <c r="H308" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I308" s="26" t="s">
+      <c r="I308" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J308" s="26">
+      <c r="J308" s="39">
         <v>8</v>
       </c>
       <c r="K308" s="26" t="s">
@@ -28525,16 +28521,16 @@
       <c r="F309" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G309" s="26" t="s">
+      <c r="G309" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H309" s="26" t="s">
+      <c r="H309" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I309" s="26" t="s">
+      <c r="I309" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J309" s="26">
+      <c r="J309" s="39">
         <v>8</v>
       </c>
       <c r="K309" s="26" t="s">
@@ -28611,16 +28607,16 @@
       <c r="F310" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G310" s="26" t="s">
+      <c r="G310" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H310" s="26" t="s">
+      <c r="H310" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I310" s="26" t="s">
+      <c r="I310" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J310" s="26">
+      <c r="J310" s="39">
         <v>8</v>
       </c>
       <c r="K310" s="26" t="s">
@@ -28697,16 +28693,16 @@
       <c r="F311" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G311" s="26" t="s">
+      <c r="G311" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H311" s="26" t="s">
+      <c r="H311" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I311" s="26" t="s">
+      <c r="I311" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J311" s="26">
+      <c r="J311" s="39">
         <v>8</v>
       </c>
       <c r="K311" s="26" t="s">
@@ -28783,16 +28779,16 @@
       <c r="F312" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G312" s="26" t="s">
+      <c r="G312" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H312" s="26" t="s">
+      <c r="H312" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I312" s="26" t="s">
+      <c r="I312" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J312" s="26">
+      <c r="J312" s="39">
         <v>8</v>
       </c>
       <c r="K312" s="26" t="s">
@@ -28869,16 +28865,16 @@
       <c r="F313" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G313" s="26" t="s">
+      <c r="G313" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H313" s="26" t="s">
+      <c r="H313" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I313" s="26" t="s">
+      <c r="I313" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J313" s="26">
+      <c r="J313" s="39">
         <v>8</v>
       </c>
       <c r="K313" s="26" t="s">
@@ -28955,16 +28951,16 @@
       <c r="F314" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G314" s="26" t="s">
+      <c r="G314" s="39" t="s">
         <v>397</v>
       </c>
-      <c r="H314" s="26" t="s">
+      <c r="H314" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I314" s="26" t="s">
+      <c r="I314" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="J314" s="26">
+      <c r="J314" s="39">
         <v>8</v>
       </c>
       <c r="K314" s="26" t="s">
@@ -29041,16 +29037,16 @@
       <c r="F315" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G315" s="26" t="s">
+      <c r="G315" s="39" t="s">
         <v>398</v>
       </c>
-      <c r="H315" s="26" t="s">
+      <c r="H315" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I315" s="26" t="s">
+      <c r="I315" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J315" s="26">
+      <c r="J315" s="39">
         <v>8</v>
       </c>
       <c r="K315" s="26" t="s">
@@ -29127,16 +29123,16 @@
       <c r="F316" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G316" s="26" t="s">
+      <c r="G316" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H316" s="26" t="s">
+      <c r="H316" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I316" s="26" t="s">
+      <c r="I316" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J316" s="26">
+      <c r="J316" s="39">
         <v>8</v>
       </c>
       <c r="K316" s="26" t="s">
@@ -29213,16 +29209,16 @@
       <c r="F317" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G317" s="26" t="s">
+      <c r="G317" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H317" s="26" t="s">
+      <c r="H317" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I317" s="26" t="s">
+      <c r="I317" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J317" s="26">
+      <c r="J317" s="39">
         <v>8</v>
       </c>
       <c r="K317" s="26" t="s">
@@ -29299,16 +29295,16 @@
       <c r="F318" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G318" s="26" t="s">
+      <c r="G318" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="H318" s="26" t="s">
+      <c r="H318" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I318" s="26" t="s">
+      <c r="I318" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J318" s="26">
+      <c r="J318" s="39">
         <v>8</v>
       </c>
       <c r="K318" s="26" t="s">
@@ -29382,16 +29378,16 @@
       <c r="F319" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G319" s="26" t="s">
+      <c r="G319" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H319" s="26" t="s">
+      <c r="H319" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I319" s="26" t="s">
+      <c r="I319" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J319" s="26">
+      <c r="J319" s="39">
         <v>8</v>
       </c>
       <c r="K319" s="26" t="s">
@@ -29465,16 +29461,16 @@
       <c r="F320" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G320" s="26" t="s">
+      <c r="G320" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H320" s="26" t="s">
+      <c r="H320" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I320" s="26" t="s">
+      <c r="I320" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J320" s="26">
+      <c r="J320" s="39">
         <v>8</v>
       </c>
       <c r="K320" s="26" t="s">
@@ -29548,16 +29544,16 @@
       <c r="F321" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G321" s="26" t="s">
+      <c r="G321" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H321" s="26" t="s">
+      <c r="H321" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I321" s="26" t="s">
+      <c r="I321" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J321" s="26">
+      <c r="J321" s="39">
         <v>8</v>
       </c>
       <c r="K321" s="26" t="s">
@@ -29631,16 +29627,16 @@
       <c r="F322" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G322" s="26" t="s">
+      <c r="G322" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H322" s="26" t="s">
+      <c r="H322" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I322" s="26" t="s">
+      <c r="I322" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J322" s="26">
+      <c r="J322" s="39">
         <v>8</v>
       </c>
       <c r="K322" s="26" t="s">
@@ -29714,16 +29710,16 @@
       <c r="F323" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G323" s="26" t="s">
+      <c r="G323" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H323" s="26" t="s">
+      <c r="H323" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I323" s="26" t="s">
+      <c r="I323" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J323" s="26">
+      <c r="J323" s="39">
         <v>8</v>
       </c>
       <c r="K323" s="26" t="s">
@@ -29797,16 +29793,16 @@
       <c r="F324" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G324" s="26" t="s">
+      <c r="G324" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H324" s="26" t="s">
+      <c r="H324" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I324" s="26" t="s">
+      <c r="I324" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J324" s="26">
+      <c r="J324" s="39">
         <v>8</v>
       </c>
       <c r="K324" s="26" t="s">
@@ -29880,16 +29876,16 @@
       <c r="F325" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G325" s="26" t="s">
+      <c r="G325" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H325" s="26" t="s">
+      <c r="H325" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I325" s="26" t="s">
+      <c r="I325" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J325" s="26">
+      <c r="J325" s="39">
         <v>8</v>
       </c>
       <c r="K325" s="26" t="s">
@@ -29963,16 +29959,16 @@
       <c r="F326" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G326" s="26" t="s">
+      <c r="G326" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H326" s="26" t="s">
+      <c r="H326" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I326" s="26" t="s">
+      <c r="I326" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J326" s="26">
+      <c r="J326" s="39">
         <v>8</v>
       </c>
       <c r="K326" s="26" t="s">
@@ -30046,16 +30042,16 @@
       <c r="F327" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G327" s="26" t="s">
+      <c r="G327" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="H327" s="26" t="s">
+      <c r="H327" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I327" s="26" t="s">
+      <c r="I327" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J327" s="26">
+      <c r="J327" s="39">
         <v>104</v>
       </c>
       <c r="K327" s="26" t="s">
@@ -30129,16 +30125,16 @@
       <c r="F328" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G328" s="26" t="s">
+      <c r="G328" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H328" s="26" t="s">
+      <c r="H328" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I328" s="26" t="s">
+      <c r="I328" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J328" s="26">
+      <c r="J328" s="39">
         <v>104</v>
       </c>
       <c r="K328" s="26" t="s">
@@ -30212,16 +30208,16 @@
       <c r="F329" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G329" s="26" t="s">
+      <c r="G329" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H329" s="26" t="s">
+      <c r="H329" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I329" s="26" t="s">
+      <c r="I329" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J329" s="26">
+      <c r="J329" s="39">
         <v>104</v>
       </c>
       <c r="K329" s="26" t="s">
@@ -30295,16 +30291,16 @@
       <c r="F330" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G330" s="26" t="s">
+      <c r="G330" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H330" s="26" t="s">
+      <c r="H330" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I330" s="26" t="s">
+      <c r="I330" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J330" s="26">
+      <c r="J330" s="39">
         <v>104</v>
       </c>
       <c r="K330" s="26" t="s">
@@ -30378,16 +30374,16 @@
       <c r="F331" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G331" s="26" t="s">
+      <c r="G331" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H331" s="26" t="s">
+      <c r="H331" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I331" s="26" t="s">
+      <c r="I331" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J331" s="26">
+      <c r="J331" s="39">
         <v>104</v>
       </c>
       <c r="K331" s="26" t="s">
@@ -30461,16 +30457,16 @@
       <c r="F332" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G332" s="26" t="s">
+      <c r="G332" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H332" s="26" t="s">
+      <c r="H332" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I332" s="26" t="s">
+      <c r="I332" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J332" s="26">
+      <c r="J332" s="39">
         <v>104</v>
       </c>
       <c r="K332" s="26" t="s">
@@ -30544,16 +30540,16 @@
       <c r="F333" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G333" s="26" t="s">
+      <c r="G333" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H333" s="26" t="s">
+      <c r="H333" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I333" s="26" t="s">
+      <c r="I333" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J333" s="26">
+      <c r="J333" s="39">
         <v>104</v>
       </c>
       <c r="K333" s="26" t="s">
@@ -30627,16 +30623,16 @@
       <c r="F334" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G334" s="26" t="s">
+      <c r="G334" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H334" s="26" t="s">
+      <c r="H334" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I334" s="26" t="s">
+      <c r="I334" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J334" s="26">
+      <c r="J334" s="39">
         <v>104</v>
       </c>
       <c r="K334" s="26" t="s">
@@ -30710,16 +30706,16 @@
       <c r="F335" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G335" s="26" t="s">
+      <c r="G335" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H335" s="26" t="s">
+      <c r="H335" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I335" s="26" t="s">
+      <c r="I335" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J335" s="26">
+      <c r="J335" s="39">
         <v>104</v>
       </c>
       <c r="K335" s="26" t="s">
@@ -30796,13 +30792,13 @@
       <c r="G336" s="39" t="s">
         <v>462</v>
       </c>
-      <c r="H336" s="26" t="s">
+      <c r="H336" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I336" s="26" t="s">
+      <c r="I336" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J336" s="26">
+      <c r="J336" s="39">
         <v>18</v>
       </c>
       <c r="K336" s="26" t="s">
@@ -30876,16 +30872,16 @@
       <c r="F337" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G337" s="26" t="s">
+      <c r="G337" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H337" s="26" t="s">
+      <c r="H337" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I337" s="26" t="s">
+      <c r="I337" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J337" s="26">
+      <c r="J337" s="39">
         <v>18</v>
       </c>
       <c r="K337" s="26" t="s">
@@ -30962,13 +30958,13 @@
       <c r="G338" s="39" t="s">
         <v>463</v>
       </c>
-      <c r="H338" s="26" t="s">
+      <c r="H338" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I338" s="26" t="s">
+      <c r="I338" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J338" s="26">
+      <c r="J338" s="39">
         <v>18</v>
       </c>
       <c r="K338" s="26" t="s">
@@ -31042,16 +31038,16 @@
       <c r="F339" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G339" s="26" t="s">
+      <c r="G339" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H339" s="26" t="s">
+      <c r="H339" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I339" s="26" t="s">
+      <c r="I339" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J339" s="26">
+      <c r="J339" s="39">
         <v>18</v>
       </c>
       <c r="K339" s="26" t="s">
@@ -31125,16 +31121,16 @@
       <c r="F340" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G340" s="26" t="s">
+      <c r="G340" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H340" s="26" t="s">
+      <c r="H340" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I340" s="26" t="s">
+      <c r="I340" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J340" s="26">
+      <c r="J340" s="39">
         <v>18</v>
       </c>
       <c r="K340" s="26" t="s">
@@ -31208,16 +31204,16 @@
       <c r="F341" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G341" s="26" t="s">
+      <c r="G341" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H341" s="26" t="s">
+      <c r="H341" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I341" s="26" t="s">
+      <c r="I341" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J341" s="26">
+      <c r="J341" s="39">
         <v>18</v>
       </c>
       <c r="K341" s="26" t="s">
@@ -31291,16 +31287,16 @@
       <c r="F342" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G342" s="26" t="s">
+      <c r="G342" s="39" t="s">
         <v>398</v>
       </c>
-      <c r="H342" s="26" t="s">
+      <c r="H342" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I342" s="26" t="s">
+      <c r="I342" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J342" s="26">
+      <c r="J342" s="39">
         <v>18</v>
       </c>
       <c r="K342" s="26" t="s">
@@ -31374,16 +31370,16 @@
       <c r="F343" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G343" s="26" t="s">
+      <c r="G343" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H343" s="26" t="s">
+      <c r="H343" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I343" s="26" t="s">
+      <c r="I343" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J343" s="26">
+      <c r="J343" s="39">
         <v>18</v>
       </c>
       <c r="K343" s="26" t="s">
@@ -31457,16 +31453,16 @@
       <c r="F344" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G344" s="26" t="s">
+      <c r="G344" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H344" s="26" t="s">
+      <c r="H344" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I344" s="26" t="s">
+      <c r="I344" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J344" s="26">
+      <c r="J344" s="39">
         <v>18</v>
       </c>
       <c r="K344" s="26" t="s">
@@ -31540,16 +31536,16 @@
       <c r="F345" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G345" s="26" t="s">
+      <c r="G345" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H345" s="26" t="s">
+      <c r="H345" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I345" s="26" t="s">
+      <c r="I345" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J345" s="26">
+      <c r="J345" s="39">
         <v>18</v>
       </c>
       <c r="K345" s="26" t="s">
@@ -31623,16 +31619,16 @@
       <c r="F346" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G346" s="26" t="s">
+      <c r="G346" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H346" s="26" t="s">
+      <c r="H346" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I346" s="26" t="s">
+      <c r="I346" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="J346" s="26">
+      <c r="J346" s="39">
         <v>12</v>
       </c>
       <c r="K346" s="26" t="s">
@@ -31703,16 +31699,16 @@
       <c r="F347" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G347" s="26" t="s">
+      <c r="G347" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H347" s="26" t="s">
+      <c r="H347" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I347" s="26" t="s">
+      <c r="I347" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J347" s="26">
+      <c r="J347" s="39">
         <v>12</v>
       </c>
       <c r="K347" s="26" t="s">
@@ -31789,16 +31785,16 @@
       <c r="F348" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G348" s="26" t="s">
+      <c r="G348" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H348" s="26" t="s">
+      <c r="H348" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I348" s="26" t="s">
+      <c r="I348" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J348" s="26">
+      <c r="J348" s="39">
         <v>12</v>
       </c>
       <c r="K348" s="26" t="s">
@@ -31875,16 +31871,16 @@
       <c r="F349" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G349" s="26" t="s">
+      <c r="G349" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="H349" s="26" t="s">
+      <c r="H349" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I349" s="26" t="s">
+      <c r="I349" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J349" s="26">
+      <c r="J349" s="39">
         <v>12</v>
       </c>
       <c r="K349" s="26" t="s">
@@ -31961,16 +31957,16 @@
       <c r="F350" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G350" s="26" t="s">
+      <c r="G350" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="H350" s="26" t="s">
+      <c r="H350" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I350" s="26" t="s">
+      <c r="I350" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J350" s="26">
+      <c r="J350" s="39">
         <v>12</v>
       </c>
       <c r="K350" s="26" t="s">
@@ -32047,16 +32043,16 @@
       <c r="F351" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G351" s="26" t="s">
+      <c r="G351" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H351" s="26" t="s">
+      <c r="H351" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I351" s="26" t="s">
+      <c r="I351" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="J351" s="26">
+      <c r="J351" s="39">
         <v>20</v>
       </c>
       <c r="K351" s="26" t="s">
@@ -32127,16 +32123,16 @@
       <c r="F352" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G352" s="26" t="s">
+      <c r="G352" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="H352" s="26" t="s">
+      <c r="H352" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I352" s="26" t="s">
+      <c r="I352" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="J352" s="26">
+      <c r="J352" s="39">
         <v>20</v>
       </c>
       <c r="K352" s="26" t="s">
@@ -32213,16 +32209,16 @@
       <c r="F353" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G353" s="26" t="s">
+      <c r="G353" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="H353" s="26" t="s">
+      <c r="H353" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I353" s="26" t="s">
+      <c r="I353" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J353" s="26">
+      <c r="J353" s="39">
         <v>20</v>
       </c>
       <c r="K353" s="26" t="s">
@@ -32299,16 +32295,16 @@
       <c r="F354" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G354" s="26" t="s">
+      <c r="G354" s="39" t="s">
         <v>307</v>
       </c>
       <c r="H354" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I354" s="26" t="s">
+      <c r="I354" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="J354" s="26">
+      <c r="J354" s="39">
         <v>20</v>
       </c>
       <c r="K354" s="26" t="s">
@@ -32385,16 +32381,16 @@
       <c r="F355" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G355" s="26" t="s">
+      <c r="G355" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="H355" s="26" t="s">
+      <c r="H355" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="I355" s="26" t="s">
+      <c r="I355" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J355" s="26">
+      <c r="J355" s="39">
         <v>20</v>
       </c>
       <c r="K355" s="26" t="s">
@@ -32471,16 +32467,16 @@
       <c r="F356" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G356" s="26" t="s">
+      <c r="G356" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="H356" s="26" t="s">
+      <c r="H356" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I356" s="26" t="s">
+      <c r="I356" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J356" s="26">
+      <c r="J356" s="39">
         <v>8</v>
       </c>
       <c r="K356" s="26" t="s">
@@ -32557,16 +32553,16 @@
       <c r="F357" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G357" s="26" t="s">
+      <c r="G357" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H357" s="26" t="s">
+      <c r="H357" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I357" s="26" t="s">
+      <c r="I357" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J357" s="26">
+      <c r="J357" s="39">
         <v>8</v>
       </c>
       <c r="K357" s="26" t="s">
@@ -32643,16 +32639,16 @@
       <c r="F358" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G358" s="26" t="s">
+      <c r="G358" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H358" s="26" t="s">
+      <c r="H358" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I358" s="26" t="s">
+      <c r="I358" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J358" s="26">
+      <c r="J358" s="39">
         <v>8</v>
       </c>
       <c r="K358" s="26" t="s">
@@ -32729,16 +32725,16 @@
       <c r="F359" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G359" s="26" t="s">
+      <c r="G359" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="H359" s="26" t="s">
+      <c r="H359" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I359" s="26" t="s">
+      <c r="I359" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J359" s="26">
+      <c r="J359" s="39">
         <v>8</v>
       </c>
       <c r="K359" s="26" t="s">
@@ -32815,16 +32811,16 @@
       <c r="F360" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G360" s="26" t="s">
+      <c r="G360" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H360" s="26" t="s">
+      <c r="H360" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I360" s="26" t="s">
+      <c r="I360" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J360" s="26">
+      <c r="J360" s="39">
         <v>8</v>
       </c>
       <c r="K360" s="26" t="s">
@@ -32901,16 +32897,16 @@
       <c r="F361" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G361" s="26" t="s">
+      <c r="G361" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H361" s="26" t="s">
+      <c r="H361" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I361" s="26" t="s">
+      <c r="I361" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J361" s="26">
+      <c r="J361" s="39">
         <v>8</v>
       </c>
       <c r="K361" s="26" t="s">
@@ -32987,16 +32983,16 @@
       <c r="F362" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G362" s="26" t="s">
+      <c r="G362" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="H362" s="26" t="s">
+      <c r="H362" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I362" s="26" t="s">
+      <c r="I362" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J362" s="26">
+      <c r="J362" s="39">
         <v>52</v>
       </c>
       <c r="K362" s="26" t="s">
@@ -33073,16 +33069,16 @@
       <c r="F363" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G363" s="26" t="s">
+      <c r="G363" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H363" s="26" t="s">
+      <c r="H363" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I363" s="26" t="s">
+      <c r="I363" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J363" s="26">
+      <c r="J363" s="39">
         <v>52</v>
       </c>
       <c r="K363" s="26" t="s">
@@ -33159,16 +33155,16 @@
       <c r="F364" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G364" s="26" t="s">
+      <c r="G364" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H364" s="26" t="s">
+      <c r="H364" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I364" s="26" t="s">
+      <c r="I364" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J364" s="26">
+      <c r="J364" s="39">
         <v>52</v>
       </c>
       <c r="K364" s="26" t="s">
@@ -33245,16 +33241,16 @@
       <c r="F365" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G365" s="26" t="s">
+      <c r="G365" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="H365" s="26" t="s">
+      <c r="H365" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I365" s="26" t="s">
+      <c r="I365" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J365" s="26">
+      <c r="J365" s="39">
         <v>52</v>
       </c>
       <c r="K365" s="26" t="s">
@@ -33331,16 +33327,16 @@
       <c r="F366" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G366" s="26" t="s">
+      <c r="G366" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H366" s="26" t="s">
+      <c r="H366" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I366" s="26" t="s">
+      <c r="I366" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="J366" s="26">
+      <c r="J366" s="39">
         <v>52</v>
       </c>
       <c r="K366" s="26" t="s">
@@ -33417,16 +33413,16 @@
       <c r="F367" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G367" s="26" t="s">
+      <c r="G367" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="H367" s="26" t="s">
+      <c r="H367" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I367" s="26" t="s">
+      <c r="I367" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J367" s="26">
+      <c r="J367" s="39">
         <v>52</v>
       </c>
       <c r="K367" s="26" t="s">
@@ -33503,16 +33499,16 @@
       <c r="F368" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G368" s="26" t="s">
+      <c r="G368" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="H368" s="26" t="s">
+      <c r="H368" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I368" s="26" t="s">
+      <c r="I368" s="39" t="s">
         <v>310</v>
       </c>
-      <c r="J368" s="26">
+      <c r="J368" s="39">
         <v>52</v>
       </c>
       <c r="K368" s="26" t="s">
@@ -33583,16 +33579,16 @@
       <c r="F369" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="G369" s="26" t="s">
+      <c r="G369" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H369" s="26" t="s">
+      <c r="H369" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I369" s="26" t="s">
+      <c r="I369" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="J369" s="26">
+      <c r="J369" s="39">
         <v>16</v>
       </c>
       <c r="K369" s="26" t="s">
@@ -33663,16 +33659,16 @@
       <c r="F370" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G370" s="26" t="s">
+      <c r="G370" s="39" t="s">
         <v>405</v>
       </c>
-      <c r="H370" s="26" t="s">
+      <c r="H370" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I370" s="26" t="s">
+      <c r="I370" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="J370" s="26">
+      <c r="J370" s="39">
         <v>16</v>
       </c>
       <c r="K370" s="26" t="s">
@@ -33749,16 +33745,16 @@
       <c r="F371" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G371" s="26" t="s">
+      <c r="G371" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H371" s="26" t="s">
+      <c r="H371" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I371" s="26" t="s">
+      <c r="I371" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J371" s="26">
+      <c r="J371" s="39">
         <v>16</v>
       </c>
       <c r="K371" s="26" t="s">
@@ -33835,16 +33831,16 @@
       <c r="F372" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G372" s="26" t="s">
+      <c r="G372" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="H372" s="26" t="s">
+      <c r="H372" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I372" s="26" t="s">
+      <c r="I372" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="J372" s="26">
+      <c r="J372" s="39">
         <v>16</v>
       </c>
       <c r="K372" s="26" t="s">
@@ -33921,16 +33917,16 @@
       <c r="F373" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G373" s="26" t="s">
+      <c r="G373" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H373" s="26" t="s">
+      <c r="H373" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I373" s="26" t="s">
+      <c r="I373" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="J373" s="26">
+      <c r="J373" s="39">
         <v>16</v>
       </c>
       <c r="K373" s="26" t="s">
@@ -34007,16 +34003,16 @@
       <c r="F374" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G374" s="26" t="s">
+      <c r="G374" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H374" s="26" t="s">
+      <c r="H374" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I374" s="26" t="s">
+      <c r="I374" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J374" s="26">
+      <c r="J374" s="39">
         <v>16</v>
       </c>
       <c r="K374" s="26" t="s">
@@ -34093,16 +34089,16 @@
       <c r="F375" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G375" s="26" t="s">
+      <c r="G375" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H375" s="26" t="s">
+      <c r="H375" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I375" s="26" t="s">
+      <c r="I375" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J375" s="26">
+      <c r="J375" s="39">
         <v>16</v>
       </c>
       <c r="K375" s="26" t="s">
@@ -34179,16 +34175,16 @@
       <c r="F376" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G376" s="26" t="s">
+      <c r="G376" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H376" s="26" t="s">
+      <c r="H376" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I376" s="26" t="s">
+      <c r="I376" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="J376" s="26">
+      <c r="J376" s="39">
         <v>16</v>
       </c>
       <c r="K376" s="26" t="s">
@@ -34265,16 +34261,16 @@
       <c r="F377" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G377" s="26" t="s">
+      <c r="G377" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="H377" s="26" t="s">
+      <c r="H377" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I377" s="26" t="s">
+      <c r="I377" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="J377" s="26">
+      <c r="J377" s="39">
         <v>16</v>
       </c>
       <c r="K377" s="26" t="s">
@@ -34357,16 +34353,16 @@
       <c r="F378" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G378" s="26" t="s">
+      <c r="G378" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H378" s="26" t="s">
+      <c r="H378" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I378" s="26" t="s">
+      <c r="I378" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J378" s="26">
+      <c r="J378" s="39">
         <v>8</v>
       </c>
       <c r="K378" s="26" t="s">
@@ -34449,16 +34445,16 @@
       <c r="F379" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G379" s="26" t="s">
+      <c r="G379" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H379" s="26" t="s">
+      <c r="H379" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I379" s="26" t="s">
+      <c r="I379" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J379" s="26">
+      <c r="J379" s="39">
         <v>8</v>
       </c>
       <c r="K379" s="26" t="s">
@@ -34541,16 +34537,16 @@
       <c r="F380" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G380" s="26" t="s">
+      <c r="G380" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H380" s="26" t="s">
+      <c r="H380" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I380" s="26" t="s">
+      <c r="I380" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J380" s="26">
+      <c r="J380" s="39">
         <v>8</v>
       </c>
       <c r="K380" s="26" t="s">
@@ -34633,16 +34629,16 @@
       <c r="F381" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G381" s="26" t="s">
+      <c r="G381" s="39" t="s">
         <v>409</v>
       </c>
-      <c r="H381" s="26" t="s">
+      <c r="H381" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I381" s="26" t="s">
+      <c r="I381" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J381" s="26">
+      <c r="J381" s="39">
         <v>8</v>
       </c>
       <c r="K381" s="26" t="s">
@@ -34725,16 +34721,16 @@
       <c r="F382" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G382" s="26" t="s">
+      <c r="G382" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H382" s="26" t="s">
+      <c r="H382" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I382" s="26" t="s">
+      <c r="I382" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="J382" s="26">
+      <c r="J382" s="39">
         <v>8</v>
       </c>
       <c r="K382" s="26" t="s">
@@ -34817,16 +34813,16 @@
       <c r="F383" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G383" s="26" t="s">
+      <c r="G383" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="H383" s="26" t="s">
+      <c r="H383" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I383" s="26" t="s">
+      <c r="I383" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="J383" s="26">
+      <c r="J383" s="39">
         <v>8</v>
       </c>
       <c r="K383" s="26" t="s">
@@ -34909,16 +34905,16 @@
       <c r="F384" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G384" s="26" t="s">
+      <c r="G384" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H384" s="26" t="s">
+      <c r="H384" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I384" s="26" t="s">
+      <c r="I384" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="J384" s="26">
+      <c r="J384" s="39">
         <v>8</v>
       </c>
       <c r="K384" s="26" t="s">
@@ -35001,16 +34997,16 @@
       <c r="F385" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G385" s="26" t="s">
+      <c r="G385" s="39" t="s">
         <v>409</v>
       </c>
-      <c r="H385" s="26" t="s">
+      <c r="H385" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="I385" s="26" t="s">
+      <c r="I385" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J385" s="26">
+      <c r="J385" s="39">
         <v>8</v>
       </c>
       <c r="K385" s="26" t="s">
@@ -35073,39 +35069,88 @@
       <c r="BI385" s="26" t="s">
         <v>258</v>
       </c>
+    </row>
+    <row r="386" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G386" s="39"/>
+      <c r="H386" s="39"/>
+      <c r="I386" s="39"/>
+      <c r="J386" s="39"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BD385" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6398585F-DECE-4274-A9C1-181DEC42AAFC}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="31" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="31" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="31" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="31" t="s">
         <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="40" t="s">
+        <v>466</v>
+      </c>
+      <c r="B6" s="42">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="40" t="s">
+        <v>467</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="40" t="s">
+        <v>468</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="40" t="s">
+        <v>469</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="40" t="s">
+        <v>470</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
